--- a/CFA-Stockist-HQ_Mapping_Master_Updated.xlsx
+++ b/CFA-Stockist-HQ_Mapping_Master_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milind\Desktop\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1189060-0749-4231-80A5-C7C6281B9825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{608F679D-FAC4-42E8-8BEB-B5E560AF52BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,10 @@
     <sheet name="CFA-Stockist-HQ Mapping" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CFA-Stockist-HQ Mapping'!$A$1:$AF$593</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CFA-Stockist-HQ Mapping'!$A$1:$AE$590</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12915" uniqueCount="2449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12883" uniqueCount="2444">
   <si>
     <t>Distributor Code</t>
   </si>
@@ -7364,25 +7365,10 @@
     <t>Kolkata</t>
   </si>
   <si>
-    <t>S0261</t>
-  </si>
-  <si>
-    <t>S0265</t>
-  </si>
-  <si>
-    <t>S0364</t>
-  </si>
-  <si>
-    <t>Kolkata 2</t>
-  </si>
-  <si>
-    <t>C0110</t>
-  </si>
-  <si>
-    <t>ACP PHARMACEUTCIALS</t>
-  </si>
-  <si>
-    <t>Kendrapada</t>
+    <t>C1129</t>
+  </si>
+  <si>
+    <t>NEELAM PHARMA</t>
   </si>
 </sst>
 </file>
@@ -7492,17 +7478,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFBDD7EE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBDD7EE"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="hair">
         <color rgb="FF000000"/>
       </left>
@@ -7517,11 +7492,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDD7EE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBDD7EE"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7540,14 +7526,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7851,8 +7834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AF630"/>
+  <dimension ref="A1:AE630"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1796875" customWidth="1"/>
@@ -7979,7 +7961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -8044,7 +8026,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -8109,7 +8091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -8174,7 +8156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -8243,7 +8225,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
@@ -8312,7 +8294,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
@@ -8381,7 +8363,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -8450,7 +8432,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
@@ -8519,7 +8501,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -8600,7 +8582,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>32</v>
       </c>
@@ -8681,7 +8663,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -8762,7 +8744,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -9086,7 +9068,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -9167,7 +9149,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -9248,7 +9230,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -9329,7 +9311,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
@@ -9410,7 +9392,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
@@ -9495,7 +9477,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -9580,7 +9562,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>32</v>
       </c>
@@ -9665,7 +9647,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -9750,7 +9732,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>32</v>
       </c>
@@ -9835,7 +9817,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>32</v>
       </c>
@@ -9920,7 +9902,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
@@ -10001,7 +9983,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
@@ -10082,7 +10064,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
@@ -10163,7 +10145,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -10244,7 +10226,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
@@ -10325,7 +10307,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -10406,7 +10388,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
@@ -10487,7 +10469,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -10564,7 +10546,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
@@ -10641,7 +10623,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -10718,7 +10700,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>32</v>
       </c>
@@ -10795,7 +10777,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
@@ -10876,7 +10858,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>32</v>
       </c>
@@ -10955,7 +10937,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
@@ -11036,7 +11018,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
@@ -11111,7 +11093,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>32</v>
       </c>
@@ -11192,7 +11174,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>32</v>
       </c>
@@ -11273,7 +11255,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>32</v>
       </c>
@@ -11354,7 +11336,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>32</v>
       </c>
@@ -11435,7 +11417,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>32</v>
       </c>
@@ -11512,7 +11494,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>32</v>
       </c>
@@ -11593,7 +11575,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>204</v>
       </c>
@@ -11664,7 +11646,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>204</v>
       </c>
@@ -11735,7 +11717,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>204</v>
       </c>
@@ -11806,7 +11788,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>204</v>
       </c>
@@ -11881,7 +11863,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>204</v>
       </c>
@@ -11956,7 +11938,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>204</v>
       </c>
@@ -12031,7 +12013,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>204</v>
       </c>
@@ -12106,7 +12088,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>204</v>
       </c>
@@ -12181,7 +12163,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>204</v>
       </c>
@@ -12256,7 +12238,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>204</v>
       </c>
@@ -12327,7 +12309,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>204</v>
       </c>
@@ -12398,7 +12380,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>204</v>
       </c>
@@ -12473,7 +12455,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>204</v>
       </c>
@@ -12548,7 +12530,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>204</v>
       </c>
@@ -12623,7 +12605,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="62" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>204</v>
       </c>
@@ -12698,7 +12680,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="63" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>204</v>
       </c>
@@ -12773,7 +12755,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>204</v>
       </c>
@@ -12844,7 +12826,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>204</v>
       </c>
@@ -12915,7 +12897,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>204</v>
       </c>
@@ -12990,7 +12972,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>204</v>
       </c>
@@ -13065,7 +13047,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>204</v>
       </c>
@@ -13140,7 +13122,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>292</v>
       </c>
@@ -13221,7 +13203,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>292</v>
       </c>
@@ -13302,7 +13284,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>292</v>
       </c>
@@ -13383,7 +13365,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>292</v>
       </c>
@@ -13464,7 +13446,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>292</v>
       </c>
@@ -13545,7 +13527,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>292</v>
       </c>
@@ -13626,7 +13608,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>292</v>
       </c>
@@ -13701,7 +13683,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>292</v>
       </c>
@@ -13776,7 +13758,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>292</v>
       </c>
@@ -13851,7 +13833,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>292</v>
       </c>
@@ -13926,7 +13908,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>292</v>
       </c>
@@ -14001,7 +13983,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>292</v>
       </c>
@@ -14076,7 +14058,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>292</v>
       </c>
@@ -14151,7 +14133,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>292</v>
       </c>
@@ -14226,7 +14208,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>292</v>
       </c>
@@ -14301,7 +14283,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>292</v>
       </c>
@@ -14376,7 +14358,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>292</v>
       </c>
@@ -14451,7 +14433,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>292</v>
       </c>
@@ -14526,7 +14508,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>292</v>
       </c>
@@ -14601,7 +14583,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>292</v>
       </c>
@@ -14676,7 +14658,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>292</v>
       </c>
@@ -14751,7 +14733,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>292</v>
       </c>
@@ -14826,7 +14808,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="91" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>292</v>
       </c>
@@ -14901,7 +14883,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>292</v>
       </c>
@@ -14972,7 +14954,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="93" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>292</v>
       </c>
@@ -15043,7 +15025,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="94" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>292</v>
       </c>
@@ -15114,7 +15096,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>292</v>
       </c>
@@ -15185,7 +15167,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>292</v>
       </c>
@@ -15256,7 +15238,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>292</v>
       </c>
@@ -15337,7 +15319,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>292</v>
       </c>
@@ -15418,7 +15400,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>292</v>
       </c>
@@ -15499,7 +15481,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>292</v>
       </c>
@@ -15580,7 +15562,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>292</v>
       </c>
@@ -15661,7 +15643,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>292</v>
       </c>
@@ -15742,7 +15724,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="103" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>292</v>
       </c>
@@ -15817,7 +15799,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>292</v>
       </c>
@@ -15892,7 +15874,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="105" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>292</v>
       </c>
@@ -15967,7 +15949,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>292</v>
       </c>
@@ -16042,7 +16024,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="107" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>292</v>
       </c>
@@ -16117,7 +16099,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="108" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>292</v>
       </c>
@@ -16192,7 +16174,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>292</v>
       </c>
@@ -16267,7 +16249,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -16342,7 +16324,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>292</v>
       </c>
@@ -16417,7 +16399,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>292</v>
       </c>
@@ -16492,7 +16474,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>292</v>
       </c>
@@ -16567,7 +16549,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>292</v>
       </c>
@@ -16642,7 +16624,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>292</v>
       </c>
@@ -16717,7 +16699,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>292</v>
       </c>
@@ -16792,7 +16774,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>292</v>
       </c>
@@ -16867,7 +16849,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="118" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>292</v>
       </c>
@@ -16948,7 +16930,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="119" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>292</v>
       </c>
@@ -17029,7 +17011,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>292</v>
       </c>
@@ -17110,7 +17092,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>292</v>
       </c>
@@ -17181,7 +17163,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>487</v>
       </c>
@@ -17260,7 +17242,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="123" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>487</v>
       </c>
@@ -17331,7 +17313,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="124" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>487</v>
       </c>
@@ -17402,7 +17384,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="125" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>487</v>
       </c>
@@ -17473,7 +17455,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="126" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>487</v>
       </c>
@@ -17548,7 +17530,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="127" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>487</v>
       </c>
@@ -17619,7 +17601,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="128" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>487</v>
       </c>
@@ -17690,7 +17672,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="129" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>487</v>
       </c>
@@ -17761,7 +17743,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>487</v>
       </c>
@@ -17836,7 +17818,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>487</v>
       </c>
@@ -17911,7 +17893,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>487</v>
       </c>
@@ -17986,7 +17968,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>487</v>
       </c>
@@ -18061,7 +18043,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="134" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>487</v>
       </c>
@@ -18136,7 +18118,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>487</v>
       </c>
@@ -18211,7 +18193,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>487</v>
       </c>
@@ -18286,7 +18268,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="137" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>487</v>
       </c>
@@ -18357,7 +18339,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="138" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>487</v>
       </c>
@@ -18428,7 +18410,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="139" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>487</v>
       </c>
@@ -18499,7 +18481,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>487</v>
       </c>
@@ -18564,7 +18546,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>487</v>
       </c>
@@ -18629,7 +18611,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>487</v>
       </c>
@@ -18710,7 +18692,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>487</v>
       </c>
@@ -18791,7 +18773,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>487</v>
       </c>
@@ -18872,7 +18854,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>487</v>
       </c>
@@ -18953,7 +18935,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>594</v>
       </c>
@@ -19022,7 +19004,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>594</v>
       </c>
@@ -19091,7 +19073,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>594</v>
       </c>
@@ -19160,7 +19142,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>594</v>
       </c>
@@ -19229,7 +19211,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>594</v>
       </c>
@@ -19304,7 +19286,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
         <v>594</v>
       </c>
@@ -19379,7 +19361,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>594</v>
       </c>
@@ -19444,7 +19426,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>594</v>
       </c>
@@ -19519,7 +19501,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>594</v>
       </c>
@@ -19594,7 +19576,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
         <v>594</v>
       </c>
@@ -19659,7 +19641,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>594</v>
       </c>
@@ -19734,7 +19716,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
         <v>594</v>
       </c>
@@ -19809,7 +19791,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>594</v>
       </c>
@@ -19884,7 +19866,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
         <v>653</v>
       </c>
@@ -19965,7 +19947,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>653</v>
       </c>
@@ -20046,7 +20028,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="161" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
         <v>653</v>
       </c>
@@ -20127,7 +20109,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="162" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>653</v>
       </c>
@@ -20208,7 +20190,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="163" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>653</v>
       </c>
@@ -20289,7 +20271,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="164" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>653</v>
       </c>
@@ -20360,7 +20342,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
         <v>653</v>
       </c>
@@ -20431,7 +20413,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="166" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>653</v>
       </c>
@@ -20512,7 +20494,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="167" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>653</v>
       </c>
@@ -20587,7 +20569,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="168" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>653</v>
       </c>
@@ -20662,7 +20644,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="169" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
         <v>653</v>
       </c>
@@ -20737,7 +20719,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="170" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>653</v>
       </c>
@@ -20812,7 +20794,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>653</v>
       </c>
@@ -20887,7 +20869,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="172" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>653</v>
       </c>
@@ -20962,7 +20944,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="173" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
         <v>653</v>
       </c>
@@ -21033,7 +21015,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="174" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>653</v>
       </c>
@@ -21104,7 +21086,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
         <v>653</v>
       </c>
@@ -21175,7 +21157,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>653</v>
       </c>
@@ -21246,7 +21228,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
         <v>653</v>
       </c>
@@ -21317,7 +21299,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="178" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>653</v>
       </c>
@@ -21388,7 +21370,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="179" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
         <v>653</v>
       </c>
@@ -21459,7 +21441,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="180" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>653</v>
       </c>
@@ -21530,7 +21512,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="181" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
         <v>653</v>
       </c>
@@ -21601,7 +21583,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="182" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>653</v>
       </c>
@@ -21672,7 +21654,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="183" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>653</v>
       </c>
@@ -21743,7 +21725,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="184" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>653</v>
       </c>
@@ -21814,7 +21796,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="185" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
         <v>653</v>
       </c>
@@ -21885,7 +21867,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="186" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>653</v>
       </c>
@@ -21960,7 +21942,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="187" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
         <v>653</v>
       </c>
@@ -22035,7 +22017,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="188" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>653</v>
       </c>
@@ -22110,7 +22092,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="189" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
         <v>653</v>
       </c>
@@ -22185,7 +22167,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="190" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>653</v>
       </c>
@@ -22258,7 +22240,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="191" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
         <v>653</v>
       </c>
@@ -22333,7 +22315,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="192" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>653</v>
       </c>
@@ -22414,7 +22396,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="193" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
         <v>653</v>
       </c>
@@ -22495,7 +22477,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="194" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>653</v>
       </c>
@@ -22576,7 +22558,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="195" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
         <v>653</v>
       </c>
@@ -22657,7 +22639,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="196" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>653</v>
       </c>
@@ -22732,7 +22714,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="197" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
         <v>653</v>
       </c>
@@ -22803,7 +22785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="198" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>653</v>
       </c>
@@ -22874,7 +22856,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
         <v>653</v>
       </c>
@@ -22949,7 +22931,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="200" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
         <v>653</v>
       </c>
@@ -23024,7 +23006,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="201" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>653</v>
       </c>
@@ -23099,7 +23081,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="202" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
         <v>653</v>
       </c>
@@ -23180,7 +23162,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="203" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>653</v>
       </c>
@@ -23255,7 +23237,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="204" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
         <v>653</v>
       </c>
@@ -23330,7 +23312,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="205" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>826</v>
       </c>
@@ -23395,7 +23377,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="206" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
         <v>826</v>
       </c>
@@ -23464,7 +23446,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="207" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>826</v>
       </c>
@@ -23533,7 +23515,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="208" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
         <v>826</v>
       </c>
@@ -23602,7 +23584,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="209" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>826</v>
       </c>
@@ -23667,7 +23649,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="210" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
         <v>826</v>
       </c>
@@ -23732,7 +23714,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="211" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>826</v>
       </c>
@@ -23797,7 +23779,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="212" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
         <v>826</v>
       </c>
@@ -23866,7 +23848,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="213" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>826</v>
       </c>
@@ -23935,7 +23917,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="214" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
         <v>826</v>
       </c>
@@ -24004,7 +23986,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="215" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>826</v>
       </c>
@@ -24069,7 +24051,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="216" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
         <v>826</v>
       </c>
@@ -24134,7 +24116,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="217" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>826</v>
       </c>
@@ -24197,7 +24179,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="218" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
         <v>826</v>
       </c>
@@ -24262,7 +24244,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="219" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>826</v>
       </c>
@@ -24331,7 +24313,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="220" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
         <v>826</v>
       </c>
@@ -24400,7 +24382,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="221" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>826</v>
       </c>
@@ -24469,7 +24451,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="222" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3" t="s">
         <v>826</v>
       </c>
@@ -24538,7 +24520,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="223" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>826</v>
       </c>
@@ -24607,7 +24589,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="224" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
         <v>826</v>
       </c>
@@ -24672,7 +24654,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="225" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>826</v>
       </c>
@@ -24737,7 +24719,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="226" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
         <v>826</v>
       </c>
@@ -24802,7 +24784,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="227" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>826</v>
       </c>
@@ -24867,7 +24849,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="228" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
         <v>826</v>
       </c>
@@ -24932,7 +24914,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="229" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>826</v>
       </c>
@@ -24997,7 +24979,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="230" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>826</v>
       </c>
@@ -25062,7 +25044,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="231" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>826</v>
       </c>
@@ -25127,7 +25109,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="232" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
         <v>826</v>
       </c>
@@ -25192,7 +25174,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="233" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>943</v>
       </c>
@@ -25267,7 +25249,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="234" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
         <v>943</v>
       </c>
@@ -25342,7 +25324,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="235" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>943</v>
       </c>
@@ -25417,7 +25399,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="236" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
         <v>943</v>
       </c>
@@ -25492,7 +25474,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="237" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>943</v>
       </c>
@@ -25567,7 +25549,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="238" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
         <v>943</v>
       </c>
@@ -25642,7 +25624,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="239" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>943</v>
       </c>
@@ -25717,7 +25699,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="240" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
         <v>943</v>
       </c>
@@ -25792,7 +25774,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>943</v>
       </c>
@@ -25863,7 +25845,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="242" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
         <v>943</v>
       </c>
@@ -25934,7 +25916,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="243" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>943</v>
       </c>
@@ -26005,7 +25987,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="244" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
         <v>943</v>
       </c>
@@ -26076,7 +26058,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="245" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>943</v>
       </c>
@@ -26151,7 +26133,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="246" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
         <v>943</v>
       </c>
@@ -26226,7 +26208,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="247" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>943</v>
       </c>
@@ -26301,7 +26283,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="248" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
         <v>943</v>
       </c>
@@ -26376,7 +26358,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="249" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>943</v>
       </c>
@@ -26451,7 +26433,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="250" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
         <v>943</v>
       </c>
@@ -26532,7 +26514,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="251" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>943</v>
       </c>
@@ -26613,7 +26595,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="252" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
         <v>943</v>
       </c>
@@ -26688,7 +26670,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="253" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>943</v>
       </c>
@@ -26763,7 +26745,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="254" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
         <v>943</v>
       </c>
@@ -26838,7 +26820,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="255" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>943</v>
       </c>
@@ -26913,7 +26895,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="256" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
         <v>943</v>
       </c>
@@ -26988,7 +26970,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="257" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>943</v>
       </c>
@@ -27063,7 +27045,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="258" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
         <v>943</v>
       </c>
@@ -27138,7 +27120,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="259" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>943</v>
       </c>
@@ -27213,7 +27195,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="260" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
         <v>943</v>
       </c>
@@ -27288,7 +27270,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="261" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>943</v>
       </c>
@@ -27363,7 +27345,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="262" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
         <v>943</v>
       </c>
@@ -27438,7 +27420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="263" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>943</v>
       </c>
@@ -27513,7 +27495,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="264" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
         <v>943</v>
       </c>
@@ -27584,7 +27566,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="265" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>943</v>
       </c>
@@ -27655,7 +27637,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="266" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
         <v>943</v>
       </c>
@@ -27736,7 +27718,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="267" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>943</v>
       </c>
@@ -27817,7 +27799,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="268" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
         <v>943</v>
       </c>
@@ -27898,7 +27880,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="269" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>943</v>
       </c>
@@ -27979,7 +27961,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="270" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
         <v>943</v>
       </c>
@@ -28054,7 +28036,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="271" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>943</v>
       </c>
@@ -28129,7 +28111,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="272" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
         <v>943</v>
       </c>
@@ -28204,7 +28186,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="273" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>943</v>
       </c>
@@ -28279,7 +28261,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="274" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
         <v>943</v>
       </c>
@@ -28354,7 +28336,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="275" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>943</v>
       </c>
@@ -28437,7 +28419,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="276" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
         <v>943</v>
       </c>
@@ -28520,7 +28502,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="277" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>943</v>
       </c>
@@ -28603,7 +28585,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="278" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
         <v>943</v>
       </c>
@@ -28678,7 +28660,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="279" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>943</v>
       </c>
@@ -28753,7 +28735,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="280" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
         <v>943</v>
       </c>
@@ -28828,7 +28810,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="281" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>943</v>
       </c>
@@ -28903,7 +28885,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="282" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
         <v>943</v>
       </c>
@@ -28978,7 +28960,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="283" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>943</v>
       </c>
@@ -29053,7 +29035,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="284" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
         <v>943</v>
       </c>
@@ -29128,7 +29110,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="285" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>943</v>
       </c>
@@ -29203,7 +29185,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="286" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
         <v>943</v>
       </c>
@@ -29278,7 +29260,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="287" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>943</v>
       </c>
@@ -29353,7 +29335,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="288" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
         <v>943</v>
       </c>
@@ -29428,7 +29410,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="289" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>943</v>
       </c>
@@ -29503,7 +29485,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="290" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
         <v>943</v>
       </c>
@@ -29578,7 +29560,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="291" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>943</v>
       </c>
@@ -29653,7 +29635,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="292" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
         <v>943</v>
       </c>
@@ -29728,7 +29710,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="293" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>943</v>
       </c>
@@ -29803,7 +29785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="294" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
         <v>943</v>
       </c>
@@ -29878,7 +29860,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="295" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>943</v>
       </c>
@@ -29953,7 +29935,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="296" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
         <v>943</v>
       </c>
@@ -30028,7 +30010,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="297" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>943</v>
       </c>
@@ -30103,7 +30085,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="298" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
         <v>943</v>
       </c>
@@ -30178,7 +30160,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="299" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>943</v>
       </c>
@@ -30253,7 +30235,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="300" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
         <v>943</v>
       </c>
@@ -30328,7 +30310,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="301" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>943</v>
       </c>
@@ -30403,7 +30385,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="302" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
         <v>943</v>
       </c>
@@ -30478,7 +30460,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="303" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>943</v>
       </c>
@@ -30553,7 +30535,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="304" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
         <v>943</v>
       </c>
@@ -30628,7 +30610,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="305" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>943</v>
       </c>
@@ -30703,7 +30685,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="306" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
         <v>943</v>
       </c>
@@ -30778,7 +30760,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="307" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>943</v>
       </c>
@@ -30853,7 +30835,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="308" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
         <v>943</v>
       </c>
@@ -30928,7 +30910,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="309" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>943</v>
       </c>
@@ -31003,7 +30985,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="310" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
         <v>943</v>
       </c>
@@ -31078,7 +31060,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="311" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>943</v>
       </c>
@@ -31153,7 +31135,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="312" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
         <v>943</v>
       </c>
@@ -31228,7 +31210,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="313" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>943</v>
       </c>
@@ -31303,7 +31285,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="314" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
         <v>943</v>
       </c>
@@ -31378,7 +31360,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="315" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>943</v>
       </c>
@@ -31453,7 +31435,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="316" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
         <v>943</v>
       </c>
@@ -31528,7 +31510,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="317" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>943</v>
       </c>
@@ -31603,7 +31585,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="318" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
         <v>943</v>
       </c>
@@ -31686,7 +31668,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="319" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>943</v>
       </c>
@@ -31769,7 +31751,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="320" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
         <v>943</v>
       </c>
@@ -31852,7 +31834,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="321" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
         <v>943</v>
       </c>
@@ -31935,7 +31917,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="322" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
         <v>943</v>
       </c>
@@ -32018,7 +32000,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="323" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>943</v>
       </c>
@@ -32101,7 +32083,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="324" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
         <v>943</v>
       </c>
@@ -32184,7 +32166,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="325" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>943</v>
       </c>
@@ -32267,7 +32249,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="326" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
         <v>943</v>
       </c>
@@ -32338,7 +32320,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="327" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
         <v>943</v>
       </c>
@@ -32409,7 +32391,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="328" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
         <v>943</v>
       </c>
@@ -32480,7 +32462,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="329" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
         <v>943</v>
       </c>
@@ -32551,7 +32533,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="330" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
         <v>943</v>
       </c>
@@ -32636,7 +32618,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="331" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>943</v>
       </c>
@@ -32721,7 +32703,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="332" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="3" t="s">
         <v>943</v>
       </c>
@@ -32806,7 +32788,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="333" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>943</v>
       </c>
@@ -32891,7 +32873,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="334" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
         <v>943</v>
       </c>
@@ -32976,7 +32958,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="335" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>943</v>
       </c>
@@ -33047,7 +33029,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="336" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
         <v>943</v>
       </c>
@@ -33118,7 +33100,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="337" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
         <v>943</v>
       </c>
@@ -33193,7 +33175,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="338" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>943</v>
       </c>
@@ -33264,7 +33246,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="339" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33329,7 +33311,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33394,7 +33376,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33459,7 +33441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="342" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33524,7 +33506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="343" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33589,7 +33571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33654,7 +33636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="345" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33719,7 +33701,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="346" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33784,7 +33766,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="347" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33849,7 +33831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="348" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33914,7 +33896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="349" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33979,7 +33961,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34044,7 +34026,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="351" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34109,7 +34091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="352" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34174,7 +34156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="353" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34239,7 +34221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="354" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34304,7 +34286,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="355" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34369,7 +34351,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="356" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34434,7 +34416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="357" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34499,7 +34481,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="358" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34564,7 +34546,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="359" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="3" t="s">
         <v>1417</v>
       </c>
@@ -34629,7 +34611,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="360" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34694,7 +34676,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="361" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3" t="s">
         <v>1417</v>
       </c>
@@ -34759,7 +34741,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="362" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34824,7 +34806,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="363" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3" t="s">
         <v>1417</v>
       </c>
@@ -34889,7 +34871,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="364" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34954,7 +34936,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="365" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35019,7 +35001,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="366" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35084,7 +35066,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="367" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35149,7 +35131,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="368" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35214,7 +35196,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="369" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35279,7 +35261,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="370" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35344,7 +35326,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="371" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35409,7 +35391,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="372" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35474,7 +35456,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="373" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35539,7 +35521,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="374" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>1479</v>
       </c>
@@ -35616,7 +35598,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="375" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
         <v>1479</v>
       </c>
@@ -35693,7 +35675,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="376" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
         <v>1479</v>
       </c>
@@ -35770,7 +35752,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="377" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="3" t="s">
         <v>1479</v>
       </c>
@@ -35851,7 +35833,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="378" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
         <v>1479</v>
       </c>
@@ -35932,7 +35914,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="379" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36013,7 +35995,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="380" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36094,7 +36076,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="381" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36175,7 +36157,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="382" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36256,7 +36238,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="383" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36337,7 +36319,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="384" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36412,7 +36394,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="385" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36487,7 +36469,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="386" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36568,7 +36550,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="387" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36649,7 +36631,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="388" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36730,7 +36712,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="389" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36817,7 +36799,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="390" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36904,7 +36886,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="391" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36991,7 +36973,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="392" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37078,7 +37060,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="393" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37153,7 +37135,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="394" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37228,7 +37210,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="395" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37303,7 +37285,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="396" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37374,7 +37356,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="397" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37445,7 +37427,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="398" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37516,7 +37498,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="399" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37597,7 +37579,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="400" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37678,7 +37660,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="401" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37759,7 +37741,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="402" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37840,7 +37822,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="403" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37921,7 +37903,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="404" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38002,7 +37984,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="405" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38077,7 +38059,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="406" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38152,7 +38134,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="407" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38222,11 +38204,8 @@
       <c r="AE407" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AF407">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="408" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="408" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38297,7 +38276,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="409" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38368,7 +38347,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="410" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38451,7 +38430,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="411" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38534,7 +38513,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="412" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38609,7 +38588,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="413" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38684,7 +38663,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="414" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38759,7 +38738,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="415" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38846,7 +38825,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="416" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38933,7 +38912,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="417" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39020,7 +38999,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="418" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39101,7 +39080,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="419" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39182,7 +39161,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="420" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39263,7 +39242,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="421" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39344,7 +39323,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="422" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39425,7 +39404,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="423" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39506,7 +39485,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="424" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39587,7 +39566,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="425" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39662,7 +39641,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="426" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39737,7 +39716,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="427" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39812,7 +39791,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="428" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39887,7 +39866,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="429" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39962,7 +39941,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="430" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40037,7 +40016,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="431" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40124,7 +40103,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="432" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40199,7 +40178,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="433" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40270,7 +40249,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="434" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40341,7 +40320,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="435" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40412,7 +40391,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="436" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40487,7 +40466,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="437" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40562,7 +40541,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="438" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40643,7 +40622,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="439" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40722,7 +40701,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="440" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40801,7 +40780,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="441" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40880,7 +40859,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="442" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40959,7 +40938,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="443" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41038,7 +41017,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="444" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41117,7 +41096,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="445" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41196,7 +41175,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="446" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41279,7 +41258,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="447" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41362,7 +41341,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="448" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41445,7 +41424,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="449" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41528,7 +41507,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="450" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41611,7 +41590,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="451" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41694,7 +41673,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="452" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41777,7 +41756,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="453" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41860,7 +41839,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="454" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41947,7 +41926,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="455" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42034,7 +42013,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="456" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42121,7 +42100,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="457" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42208,7 +42187,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="458" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42295,7 +42274,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="459" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42374,7 +42353,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="460" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42453,7 +42432,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="461" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42532,7 +42511,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="462" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42611,7 +42590,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="463" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42690,7 +42669,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="464" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42769,7 +42748,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="465" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42848,7 +42827,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="466" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42937,7 +42916,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="467" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43026,7 +43005,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="468" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43115,7 +43094,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="469" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43204,7 +43183,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="470" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43293,7 +43272,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="471" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43382,7 +43361,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="472" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43471,7 +43450,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="473" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43560,7 +43539,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="474" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43649,7 +43628,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="475" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43738,7 +43717,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="476" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43815,7 +43794,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="477" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43886,7 +43865,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="478" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43959,7 +43938,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="479" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44036,7 +44015,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="480" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44123,7 +44102,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="481" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44202,7 +44181,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="482" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44276,7 +44255,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="483" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44363,7 +44342,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="484" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44450,7 +44429,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="485" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44527,7 +44506,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="486" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44614,7 +44593,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="487" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44691,7 +44670,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="488" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44770,7 +44749,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="489" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44851,7 +44830,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="490" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44928,7 +44907,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="491" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45003,7 +44982,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="492" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45083,7 +45062,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="493" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45164,7 +45143,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="494" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45241,7 +45220,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="495" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45318,7 +45297,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="496" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45393,7 +45372,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="497" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45468,7 +45447,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="498" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45545,7 +45524,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="499" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45620,7 +45599,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="500" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45701,7 +45680,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="501" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45782,7 +45761,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="502" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45859,7 +45838,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="503" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45936,7 +45915,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="504" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46021,7 +46000,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="505" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46106,7 +46085,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="506" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46191,7 +46170,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="507" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46276,7 +46255,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="508" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46361,7 +46340,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="509" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46446,7 +46425,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="510" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46531,7 +46510,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="511" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46616,7 +46595,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="512" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46701,7 +46680,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="513" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46786,7 +46765,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="514" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46871,7 +46850,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="515" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46952,7 +46931,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="516" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47033,7 +47012,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="517" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="3" t="s">
         <v>1479</v>
       </c>
@@ -47120,7 +47099,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="518" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47207,7 +47186,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="519" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="3" t="s">
         <v>1479</v>
       </c>
@@ -47290,7 +47269,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="520" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47373,7 +47352,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="521" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="3" t="s">
         <v>1479</v>
       </c>
@@ -47454,7 +47433,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="522" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47541,7 +47520,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="523" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47628,7 +47607,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="524" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="3" t="s">
         <v>2023</v>
       </c>
@@ -47705,7 +47684,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="525" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="2" t="s">
         <v>2023</v>
       </c>
@@ -47786,7 +47765,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="526" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="3" t="s">
         <v>2023</v>
       </c>
@@ -47867,7 +47846,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="527" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="2" t="s">
         <v>2023</v>
       </c>
@@ -47948,7 +47927,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="528" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48029,7 +48008,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="529" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48110,7 +48089,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="530" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48191,7 +48170,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="531" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48266,7 +48245,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="532" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48347,7 +48326,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="533" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48434,7 +48413,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="534" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48521,7 +48500,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="535" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48608,7 +48587,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="536" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48695,7 +48674,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="537" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48778,7 +48757,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="538" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48861,7 +48840,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="539" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48944,7 +48923,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="540" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49027,7 +49006,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="541" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49110,7 +49089,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="542" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49193,7 +49172,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="543" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49276,7 +49255,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="544" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49359,7 +49338,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="545" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49444,7 +49423,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="546" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49529,7 +49508,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="547" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49614,7 +49593,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="548" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49685,7 +49664,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="549" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49772,7 +49751,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="550" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49859,7 +49838,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="551" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49934,7 +49913,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="552" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50009,7 +49988,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="553" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50084,7 +50063,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="554" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50171,7 +50150,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="555" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50246,7 +50225,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="556" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50321,7 +50300,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="557" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50392,7 +50371,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="558" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50463,7 +50442,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="559" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50550,7 +50529,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="560" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50637,7 +50616,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="561" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50718,7 +50697,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="562" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50799,7 +50778,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="563" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50884,7 +50863,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="564" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50969,7 +50948,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="565" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51050,7 +51029,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="566" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51139,7 +51118,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="567" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51228,7 +51207,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="568" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51317,7 +51296,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="569" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51406,7 +51385,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="570" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51495,7 +51474,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="571" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51580,7 +51559,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="572" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51665,7 +51644,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="573" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51750,7 +51729,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="574" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51837,7 +51816,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="575" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51924,7 +51903,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="576" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52011,7 +51990,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="577" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52094,7 +52073,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="578" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52173,7 +52152,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="579" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52247,7 +52226,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="580" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52319,7 +52298,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="581" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52393,7 +52372,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="582" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52478,7 +52457,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="583" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52559,7 +52538,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="584" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52640,7 +52619,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="585" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52721,7 +52700,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="586" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52796,7 +52775,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="587" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52871,7 +52850,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="588" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52958,7 +52937,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="589" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="2" t="s">
         <v>2023</v>
       </c>
@@ -53045,31 +53024,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="590" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H590" s="8" t="s">
+    <row r="590" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A590" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B590" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C590" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D590" s="9" t="s">
         <v>2442</v>
       </c>
-      <c r="I590" s="8" t="s">
-        <v>1486</v>
-      </c>
-      <c r="T590" t="s">
-        <v>2422</v>
+      <c r="E590" s="8" t="s">
+        <v>2443</v>
+      </c>
+      <c r="H590" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="I590" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="J590" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K590" s="2"/>
+      <c r="L590" s="2"/>
+      <c r="M590" s="2" t="s">
+        <v>2323</v>
+      </c>
+      <c r="N590" s="2"/>
+      <c r="O590" s="2"/>
+      <c r="P590" s="2" t="s">
+        <v>2283</v>
+      </c>
+      <c r="Q590" s="2" t="s">
+        <v>2292</v>
+      </c>
+      <c r="R590" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S590" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="T590" s="2" t="s">
+        <v>2393</v>
       </c>
       <c r="U590" s="2" t="s">
-        <v>2433</v>
+        <v>2430</v>
       </c>
       <c r="V590" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="W590" t="s">
-        <v>2434</v>
-      </c>
-      <c r="X590" t="s">
-        <v>2435</v>
-      </c>
-      <c r="Y590" t="s">
-        <v>2441</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="W590" s="3"/>
+      <c r="X590" s="3"/>
+      <c r="Y590" s="7"/>
       <c r="Z590" t="s">
         <v>2436</v>
       </c>
@@ -53079,171 +53089,34 @@
       <c r="AB590" t="s">
         <v>2439</v>
       </c>
-      <c r="AC590" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="AD590" s="2" t="s">
-        <v>1489</v>
-      </c>
-      <c r="AE590" s="2" t="s">
+      <c r="AC590" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="AD590" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="AE590" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AF590">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="591" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H591" s="9" t="s">
-        <v>2443</v>
-      </c>
-      <c r="I591" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="T591" s="2" t="s">
-        <v>2394</v>
-      </c>
-      <c r="U591" s="2" t="s">
-        <v>2431</v>
-      </c>
-      <c r="V591" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="W591" s="3"/>
-      <c r="X591" s="3"/>
-      <c r="Y591" s="7"/>
-      <c r="Z591" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AA591" t="s">
-        <v>2437</v>
-      </c>
-      <c r="AB591" t="s">
-        <v>2439</v>
-      </c>
-      <c r="AC591" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="AD591" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="AF591">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="592" spans="1:32" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H592" s="10" t="s">
-        <v>2444</v>
-      </c>
-      <c r="I592" s="8" t="s">
-        <v>2445</v>
-      </c>
-      <c r="P592" s="6" t="s">
-        <v>2288</v>
-      </c>
-      <c r="Q592" s="6" t="s">
-        <v>2296</v>
-      </c>
-      <c r="R592" s="2" t="s">
-        <v>1866</v>
-      </c>
-      <c r="S592" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="T592" t="s">
-        <v>2422</v>
-      </c>
-      <c r="U592" s="2" t="s">
-        <v>2433</v>
-      </c>
-      <c r="V592" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="W592" t="s">
-        <v>2434</v>
-      </c>
-      <c r="X592" t="s">
-        <v>2435</v>
-      </c>
-      <c r="Y592" t="s">
-        <v>2441</v>
-      </c>
-      <c r="Z592" t="s">
-        <v>2436</v>
-      </c>
-      <c r="AA592" t="s">
-        <v>2437</v>
-      </c>
-      <c r="AB592" t="s">
-        <v>2439</v>
-      </c>
-      <c r="AC592" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="AD592" s="2" t="s">
-        <v>1489</v>
-      </c>
-      <c r="AE592" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF592">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="593" spans="1:22" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A593" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="B593" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="C593" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="D593" s="9" t="s">
-        <v>2446</v>
-      </c>
-      <c r="E593" s="10" t="s">
-        <v>2447</v>
-      </c>
-      <c r="H593" s="10" t="s">
-        <v>708</v>
-      </c>
-      <c r="I593" s="9" t="s">
-        <v>2448</v>
-      </c>
-      <c r="J593" s="4" t="s">
-        <v>2404</v>
-      </c>
-      <c r="K593" s="2"/>
-      <c r="L593" s="2"/>
-      <c r="M593" s="4" t="s">
-        <v>2405</v>
-      </c>
-      <c r="T593" s="2" t="s">
-        <v>2394</v>
-      </c>
-      <c r="U593" s="2" t="s">
-        <v>2431</v>
-      </c>
-      <c r="V593" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="594" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    </row>
+    <row r="591" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="592" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="593" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="594" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="595" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="596" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="597" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="598" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="599" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="600" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="601" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="602" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="603" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="604" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="605" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="606" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="607" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="608" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="609" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="610" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="611" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -53267,13 +53140,7 @@
     <row r="629" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="630" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:AF593" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="DARBANGA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AE590" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/CFA-Stockist-HQ_Mapping_Master_Updated.xlsx
+++ b/CFA-Stockist-HQ_Mapping_Master_Updated.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milind\Desktop\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{608F679D-FAC4-42E8-8BEB-B5E560AF52BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2024B0-A2E4-417E-B38D-D780116DDE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,9 @@
     <sheet name="CFA-Stockist-HQ Mapping" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CFA-Stockist-HQ Mapping'!$A$1:$AE$590</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CFA-Stockist-HQ Mapping'!$A$1:$AE$594</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12883" uniqueCount="2444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12972" uniqueCount="2453">
   <si>
     <t>Distributor Code</t>
   </si>
@@ -7369,6 +7368,33 @@
   </si>
   <si>
     <t>NEELAM PHARMA</t>
+  </si>
+  <si>
+    <t>C1121</t>
+  </si>
+  <si>
+    <t>N. S. MEDICAL AGENCY</t>
+  </si>
+  <si>
+    <t>C1123</t>
+  </si>
+  <si>
+    <t>SAI RADHA PHARMA(INDIA)PVT.LTD.-MLR</t>
+  </si>
+  <si>
+    <t>C1125</t>
+  </si>
+  <si>
+    <t>JYOTI MEDICAL AGENCIES</t>
+  </si>
+  <si>
+    <t>C1128</t>
+  </si>
+  <si>
+    <t>DHARMADAS MEDICAL</t>
+  </si>
+  <si>
+    <t>Vacant Bangalore</t>
   </si>
 </sst>
 </file>
@@ -7424,7 +7450,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -7503,11 +7529,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="hair">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7531,6 +7568,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7834,6 +7877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE630"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7961,7 +8005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -8026,7 +8070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -8091,7 +8135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -8156,7 +8200,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -8225,7 +8269,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
@@ -8294,7 +8338,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
@@ -8363,7 +8407,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -8432,7 +8476,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
@@ -8501,7 +8545,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -8582,7 +8626,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>32</v>
       </c>
@@ -8663,7 +8707,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -8744,7 +8788,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -8825,7 +8869,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -8906,7 +8950,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
@@ -8987,7 +9031,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -9068,7 +9112,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -9149,7 +9193,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -9230,7 +9274,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -9311,7 +9355,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
@@ -9392,7 +9436,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
@@ -9477,7 +9521,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -9562,7 +9606,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>32</v>
       </c>
@@ -9647,7 +9691,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -9732,7 +9776,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>32</v>
       </c>
@@ -9817,7 +9861,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>32</v>
       </c>
@@ -9902,7 +9946,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
@@ -9983,7 +10027,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
@@ -10064,7 +10108,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
@@ -10145,7 +10189,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -10226,7 +10270,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
@@ -10307,7 +10351,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -10388,7 +10432,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
@@ -10469,7 +10513,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -10546,7 +10590,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
@@ -10623,7 +10667,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -10700,7 +10744,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>32</v>
       </c>
@@ -10777,7 +10821,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
@@ -10858,7 +10902,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>32</v>
       </c>
@@ -10937,7 +10981,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
@@ -11018,7 +11062,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
@@ -11093,7 +11137,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>32</v>
       </c>
@@ -11174,7 +11218,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>32</v>
       </c>
@@ -11255,7 +11299,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>32</v>
       </c>
@@ -11336,7 +11380,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>32</v>
       </c>
@@ -11417,7 +11461,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>32</v>
       </c>
@@ -11494,7 +11538,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>32</v>
       </c>
@@ -11575,7 +11619,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>204</v>
       </c>
@@ -11646,7 +11690,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>204</v>
       </c>
@@ -11717,7 +11761,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>204</v>
       </c>
@@ -11788,7 +11832,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>204</v>
       </c>
@@ -11863,7 +11907,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>204</v>
       </c>
@@ -11938,7 +11982,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>204</v>
       </c>
@@ -12013,7 +12057,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>204</v>
       </c>
@@ -12088,7 +12132,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>204</v>
       </c>
@@ -12163,7 +12207,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>204</v>
       </c>
@@ -12238,7 +12282,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>204</v>
       </c>
@@ -12309,7 +12353,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>204</v>
       </c>
@@ -12380,7 +12424,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>204</v>
       </c>
@@ -12455,7 +12499,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>204</v>
       </c>
@@ -12530,7 +12574,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>204</v>
       </c>
@@ -12605,7 +12649,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="62" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>204</v>
       </c>
@@ -12680,7 +12724,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="63" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>204</v>
       </c>
@@ -12755,7 +12799,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>204</v>
       </c>
@@ -12826,7 +12870,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>204</v>
       </c>
@@ -12897,7 +12941,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>204</v>
       </c>
@@ -12972,7 +13016,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>204</v>
       </c>
@@ -13047,7 +13091,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>204</v>
       </c>
@@ -13122,7 +13166,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>292</v>
       </c>
@@ -13203,7 +13247,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>292</v>
       </c>
@@ -13284,7 +13328,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>292</v>
       </c>
@@ -13365,7 +13409,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>292</v>
       </c>
@@ -13446,7 +13490,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>292</v>
       </c>
@@ -13527,7 +13571,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>292</v>
       </c>
@@ -13608,7 +13652,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>292</v>
       </c>
@@ -13683,7 +13727,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>292</v>
       </c>
@@ -13758,7 +13802,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>292</v>
       </c>
@@ -13833,7 +13877,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>292</v>
       </c>
@@ -13908,7 +13952,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>292</v>
       </c>
@@ -13983,7 +14027,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>292</v>
       </c>
@@ -14058,7 +14102,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>292</v>
       </c>
@@ -14133,7 +14177,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>292</v>
       </c>
@@ -14208,7 +14252,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>292</v>
       </c>
@@ -14283,7 +14327,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>292</v>
       </c>
@@ -14358,7 +14402,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>292</v>
       </c>
@@ -14433,7 +14477,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>292</v>
       </c>
@@ -14508,7 +14552,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>292</v>
       </c>
@@ -14583,7 +14627,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>292</v>
       </c>
@@ -14658,7 +14702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>292</v>
       </c>
@@ -14733,7 +14777,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>292</v>
       </c>
@@ -14808,7 +14852,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="91" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>292</v>
       </c>
@@ -14883,7 +14927,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>292</v>
       </c>
@@ -14954,7 +14998,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="93" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>292</v>
       </c>
@@ -15025,7 +15069,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="94" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>292</v>
       </c>
@@ -15096,7 +15140,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>292</v>
       </c>
@@ -15167,7 +15211,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>292</v>
       </c>
@@ -15238,7 +15282,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>292</v>
       </c>
@@ -15319,7 +15363,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>292</v>
       </c>
@@ -15400,7 +15444,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>292</v>
       </c>
@@ -15481,7 +15525,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>292</v>
       </c>
@@ -15562,7 +15606,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>292</v>
       </c>
@@ -15643,7 +15687,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>292</v>
       </c>
@@ -15724,7 +15768,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="103" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>292</v>
       </c>
@@ -15799,7 +15843,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>292</v>
       </c>
@@ -15874,7 +15918,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="105" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>292</v>
       </c>
@@ -15949,7 +15993,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>292</v>
       </c>
@@ -16024,7 +16068,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="107" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>292</v>
       </c>
@@ -16099,7 +16143,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="108" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>292</v>
       </c>
@@ -16174,7 +16218,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>292</v>
       </c>
@@ -16249,7 +16293,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -16324,7 +16368,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>292</v>
       </c>
@@ -16399,7 +16443,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>292</v>
       </c>
@@ -16474,7 +16518,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>292</v>
       </c>
@@ -16549,7 +16593,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>292</v>
       </c>
@@ -16624,7 +16668,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>292</v>
       </c>
@@ -16699,7 +16743,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>292</v>
       </c>
@@ -16774,7 +16818,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>292</v>
       </c>
@@ -16849,7 +16893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="118" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>292</v>
       </c>
@@ -16930,7 +16974,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="119" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>292</v>
       </c>
@@ -17011,7 +17055,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>292</v>
       </c>
@@ -17092,7 +17136,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>292</v>
       </c>
@@ -17163,7 +17207,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>487</v>
       </c>
@@ -17242,7 +17286,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="123" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>487</v>
       </c>
@@ -17313,7 +17357,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="124" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>487</v>
       </c>
@@ -17384,7 +17428,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="125" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>487</v>
       </c>
@@ -17455,7 +17499,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="126" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>487</v>
       </c>
@@ -17561,7 +17605,9 @@
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
-      <c r="M127" s="2"/>
+      <c r="M127" s="2" t="s">
+        <v>2452</v>
+      </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" s="2" t="s">
@@ -17632,7 +17678,9 @@
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
+      <c r="M128" s="2" t="s">
+        <v>2452</v>
+      </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" s="2" t="s">
@@ -17703,7 +17751,9 @@
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
-      <c r="M129" s="2"/>
+      <c r="M129" s="2" t="s">
+        <v>2452</v>
+      </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" s="2" t="s">
@@ -17743,7 +17793,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>487</v>
       </c>
@@ -17818,7 +17868,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>487</v>
       </c>
@@ -17893,7 +17943,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>487</v>
       </c>
@@ -17968,7 +18018,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>487</v>
       </c>
@@ -18043,7 +18093,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="134" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>487</v>
       </c>
@@ -18118,7 +18168,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>487</v>
       </c>
@@ -18193,7 +18243,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>487</v>
       </c>
@@ -18268,7 +18318,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="137" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>487</v>
       </c>
@@ -18370,7 +18420,9 @@
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
-      <c r="M138" s="2"/>
+      <c r="M138" s="2" t="s">
+        <v>2452</v>
+      </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" s="2" t="s">
@@ -18441,7 +18493,9 @@
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
-      <c r="M139" s="2"/>
+      <c r="M139" s="2" t="s">
+        <v>2452</v>
+      </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" s="2" t="s">
@@ -18481,7 +18535,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>487</v>
       </c>
@@ -18546,7 +18600,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>487</v>
       </c>
@@ -18611,7 +18665,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>487</v>
       </c>
@@ -18692,7 +18746,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>487</v>
       </c>
@@ -18773,7 +18827,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>487</v>
       </c>
@@ -18854,7 +18908,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>487</v>
       </c>
@@ -18935,7 +18989,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>594</v>
       </c>
@@ -19004,7 +19058,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>594</v>
       </c>
@@ -19073,7 +19127,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>594</v>
       </c>
@@ -19142,7 +19196,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>594</v>
       </c>
@@ -19211,7 +19265,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>594</v>
       </c>
@@ -19286,7 +19340,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
         <v>594</v>
       </c>
@@ -19361,7 +19415,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>594</v>
       </c>
@@ -19426,7 +19480,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>594</v>
       </c>
@@ -19501,7 +19555,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>594</v>
       </c>
@@ -19576,7 +19630,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
         <v>594</v>
       </c>
@@ -19641,7 +19695,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>594</v>
       </c>
@@ -19716,7 +19770,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
         <v>594</v>
       </c>
@@ -19791,7 +19845,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>594</v>
       </c>
@@ -19866,7 +19920,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
         <v>653</v>
       </c>
@@ -19947,7 +20001,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>653</v>
       </c>
@@ -20028,7 +20082,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="161" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
         <v>653</v>
       </c>
@@ -20109,7 +20163,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="162" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>653</v>
       </c>
@@ -20190,7 +20244,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="163" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>653</v>
       </c>
@@ -20271,7 +20325,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="164" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>653</v>
       </c>
@@ -20342,7 +20396,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
         <v>653</v>
       </c>
@@ -20413,7 +20467,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="166" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>653</v>
       </c>
@@ -20494,7 +20548,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="167" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>653</v>
       </c>
@@ -20569,7 +20623,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="168" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>653</v>
       </c>
@@ -20644,7 +20698,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="169" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
         <v>653</v>
       </c>
@@ -20719,7 +20773,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="170" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>653</v>
       </c>
@@ -20794,7 +20848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>653</v>
       </c>
@@ -20869,7 +20923,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="172" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>653</v>
       </c>
@@ -20944,7 +20998,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="173" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
         <v>653</v>
       </c>
@@ -21015,7 +21069,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="174" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>653</v>
       </c>
@@ -21086,7 +21140,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
         <v>653</v>
       </c>
@@ -21157,7 +21211,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>653</v>
       </c>
@@ -21228,7 +21282,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
         <v>653</v>
       </c>
@@ -21299,7 +21353,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="178" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>653</v>
       </c>
@@ -21370,7 +21424,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="179" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
         <v>653</v>
       </c>
@@ -21441,7 +21495,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="180" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>653</v>
       </c>
@@ -21512,7 +21566,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="181" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
         <v>653</v>
       </c>
@@ -21583,7 +21637,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="182" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>653</v>
       </c>
@@ -21654,7 +21708,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="183" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>653</v>
       </c>
@@ -21725,7 +21779,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="184" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>653</v>
       </c>
@@ -21796,7 +21850,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="185" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
         <v>653</v>
       </c>
@@ -21867,7 +21921,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="186" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>653</v>
       </c>
@@ -21942,7 +21996,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="187" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
         <v>653</v>
       </c>
@@ -22017,7 +22071,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="188" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>653</v>
       </c>
@@ -22092,7 +22146,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="189" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
         <v>653</v>
       </c>
@@ -22167,7 +22221,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="190" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>653</v>
       </c>
@@ -22240,7 +22294,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="191" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
         <v>653</v>
       </c>
@@ -22315,7 +22369,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="192" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>653</v>
       </c>
@@ -22396,7 +22450,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="193" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
         <v>653</v>
       </c>
@@ -22477,7 +22531,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="194" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>653</v>
       </c>
@@ -22558,7 +22612,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="195" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
         <v>653</v>
       </c>
@@ -22639,7 +22693,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="196" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>653</v>
       </c>
@@ -22714,7 +22768,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="197" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
         <v>653</v>
       </c>
@@ -22785,7 +22839,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="198" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>653</v>
       </c>
@@ -22856,7 +22910,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
         <v>653</v>
       </c>
@@ -22931,7 +22985,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="200" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
         <v>653</v>
       </c>
@@ -23006,7 +23060,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="201" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>653</v>
       </c>
@@ -23081,7 +23135,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="202" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
         <v>653</v>
       </c>
@@ -23162,7 +23216,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="203" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>653</v>
       </c>
@@ -23237,7 +23291,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="204" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
         <v>653</v>
       </c>
@@ -23312,7 +23366,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="205" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>826</v>
       </c>
@@ -23377,7 +23431,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="206" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
         <v>826</v>
       </c>
@@ -23446,7 +23500,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="207" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>826</v>
       </c>
@@ -23515,7 +23569,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="208" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
         <v>826</v>
       </c>
@@ -23584,7 +23638,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="209" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>826</v>
       </c>
@@ -23649,7 +23703,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="210" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
         <v>826</v>
       </c>
@@ -23714,7 +23768,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="211" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>826</v>
       </c>
@@ -23779,7 +23833,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="212" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
         <v>826</v>
       </c>
@@ -23848,7 +23902,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="213" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>826</v>
       </c>
@@ -23917,7 +23971,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="214" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
         <v>826</v>
       </c>
@@ -23986,7 +24040,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="215" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>826</v>
       </c>
@@ -24051,7 +24105,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="216" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
         <v>826</v>
       </c>
@@ -24116,7 +24170,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="217" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>826</v>
       </c>
@@ -24179,7 +24233,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="218" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
         <v>826</v>
       </c>
@@ -24244,7 +24298,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="219" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>826</v>
       </c>
@@ -24313,7 +24367,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="220" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
         <v>826</v>
       </c>
@@ -24382,7 +24436,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="221" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>826</v>
       </c>
@@ -24451,7 +24505,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="222" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3" t="s">
         <v>826</v>
       </c>
@@ -24520,7 +24574,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="223" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>826</v>
       </c>
@@ -24589,7 +24643,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="224" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
         <v>826</v>
       </c>
@@ -24654,7 +24708,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="225" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>826</v>
       </c>
@@ -24719,7 +24773,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="226" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
         <v>826</v>
       </c>
@@ -24784,7 +24838,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="227" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>826</v>
       </c>
@@ -24849,7 +24903,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="228" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
         <v>826</v>
       </c>
@@ -24914,7 +24968,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="229" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>826</v>
       </c>
@@ -24979,7 +25033,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="230" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>826</v>
       </c>
@@ -25044,7 +25098,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="231" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>826</v>
       </c>
@@ -25109,7 +25163,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="232" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
         <v>826</v>
       </c>
@@ -25174,7 +25228,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="233" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>943</v>
       </c>
@@ -25249,7 +25303,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="234" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
         <v>943</v>
       </c>
@@ -25324,7 +25378,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>943</v>
       </c>
@@ -25399,7 +25453,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
         <v>943</v>
       </c>
@@ -25474,7 +25528,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>943</v>
       </c>
@@ -25549,7 +25603,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
         <v>943</v>
       </c>
@@ -25624,7 +25678,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="239" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>943</v>
       </c>
@@ -25699,7 +25753,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="240" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
         <v>943</v>
       </c>
@@ -25774,7 +25828,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>943</v>
       </c>
@@ -25845,7 +25899,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="242" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
         <v>943</v>
       </c>
@@ -25916,7 +25970,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="243" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>943</v>
       </c>
@@ -25987,7 +26041,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="244" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
         <v>943</v>
       </c>
@@ -26058,7 +26112,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>943</v>
       </c>
@@ -26133,7 +26187,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
         <v>943</v>
       </c>
@@ -26208,7 +26262,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>943</v>
       </c>
@@ -26283,7 +26337,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="248" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
         <v>943</v>
       </c>
@@ -26358,7 +26412,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="249" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>943</v>
       </c>
@@ -26433,7 +26487,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="250" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
         <v>943</v>
       </c>
@@ -26514,7 +26568,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="251" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>943</v>
       </c>
@@ -26595,7 +26649,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="252" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
         <v>943</v>
       </c>
@@ -26670,7 +26724,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="253" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>943</v>
       </c>
@@ -26745,7 +26799,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="254" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
         <v>943</v>
       </c>
@@ -26820,7 +26874,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="255" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>943</v>
       </c>
@@ -26895,7 +26949,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="256" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
         <v>943</v>
       </c>
@@ -26970,7 +27024,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="257" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>943</v>
       </c>
@@ -27045,7 +27099,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="258" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
         <v>943</v>
       </c>
@@ -27120,7 +27174,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="259" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>943</v>
       </c>
@@ -27195,7 +27249,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="260" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
         <v>943</v>
       </c>
@@ -27270,7 +27324,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="261" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>943</v>
       </c>
@@ -27345,7 +27399,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="262" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
         <v>943</v>
       </c>
@@ -27420,7 +27474,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="263" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>943</v>
       </c>
@@ -27495,7 +27549,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="264" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
         <v>943</v>
       </c>
@@ -27566,7 +27620,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="265" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>943</v>
       </c>
@@ -27637,7 +27691,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="266" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
         <v>943</v>
       </c>
@@ -27718,7 +27772,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>943</v>
       </c>
@@ -27799,7 +27853,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="268" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
         <v>943</v>
       </c>
@@ -27880,7 +27934,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="269" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>943</v>
       </c>
@@ -27961,7 +28015,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="270" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
         <v>943</v>
       </c>
@@ -28036,7 +28090,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="271" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>943</v>
       </c>
@@ -28111,7 +28165,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="272" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
         <v>943</v>
       </c>
@@ -28186,7 +28240,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="273" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>943</v>
       </c>
@@ -28261,7 +28315,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="274" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
         <v>943</v>
       </c>
@@ -28336,7 +28390,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="275" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>943</v>
       </c>
@@ -28419,7 +28473,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="276" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
         <v>943</v>
       </c>
@@ -28502,7 +28556,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="277" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>943</v>
       </c>
@@ -28585,7 +28639,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="278" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
         <v>943</v>
       </c>
@@ -28660,7 +28714,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="279" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>943</v>
       </c>
@@ -28735,7 +28789,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
         <v>943</v>
       </c>
@@ -28810,7 +28864,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>943</v>
       </c>
@@ -28885,7 +28939,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="282" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
         <v>943</v>
       </c>
@@ -28960,7 +29014,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="283" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>943</v>
       </c>
@@ -29035,7 +29089,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="284" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
         <v>943</v>
       </c>
@@ -29110,7 +29164,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="285" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>943</v>
       </c>
@@ -29185,7 +29239,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="286" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
         <v>943</v>
       </c>
@@ -29260,7 +29314,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="287" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>943</v>
       </c>
@@ -29335,7 +29389,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="288" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
         <v>943</v>
       </c>
@@ -29410,7 +29464,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="289" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>943</v>
       </c>
@@ -29485,7 +29539,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="290" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
         <v>943</v>
       </c>
@@ -29560,7 +29614,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="291" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>943</v>
       </c>
@@ -29635,7 +29689,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="292" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
         <v>943</v>
       </c>
@@ -29710,7 +29764,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>943</v>
       </c>
@@ -29785,7 +29839,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="294" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
         <v>943</v>
       </c>
@@ -29860,7 +29914,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="295" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>943</v>
       </c>
@@ -29935,7 +29989,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
         <v>943</v>
       </c>
@@ -30010,7 +30064,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="297" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>943</v>
       </c>
@@ -30085,7 +30139,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="298" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
         <v>943</v>
       </c>
@@ -30160,7 +30214,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="299" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>943</v>
       </c>
@@ -30235,7 +30289,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="300" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
         <v>943</v>
       </c>
@@ -30310,7 +30364,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="301" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>943</v>
       </c>
@@ -30385,7 +30439,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="302" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
         <v>943</v>
       </c>
@@ -30460,7 +30514,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="303" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>943</v>
       </c>
@@ -30535,7 +30589,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="304" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
         <v>943</v>
       </c>
@@ -30610,7 +30664,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="305" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>943</v>
       </c>
@@ -30685,7 +30739,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="306" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
         <v>943</v>
       </c>
@@ -30760,7 +30814,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="307" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>943</v>
       </c>
@@ -30835,7 +30889,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="308" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
         <v>943</v>
       </c>
@@ -30910,7 +30964,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="309" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>943</v>
       </c>
@@ -30985,7 +31039,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="310" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
         <v>943</v>
       </c>
@@ -31060,7 +31114,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="311" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>943</v>
       </c>
@@ -31135,7 +31189,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="312" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
         <v>943</v>
       </c>
@@ -31210,7 +31264,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="313" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>943</v>
       </c>
@@ -31285,7 +31339,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="314" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
         <v>943</v>
       </c>
@@ -31360,7 +31414,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="315" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>943</v>
       </c>
@@ -31435,7 +31489,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="316" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
         <v>943</v>
       </c>
@@ -31510,7 +31564,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="317" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>943</v>
       </c>
@@ -31585,7 +31639,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="318" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
         <v>943</v>
       </c>
@@ -31668,7 +31722,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="319" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>943</v>
       </c>
@@ -31751,7 +31805,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="320" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
         <v>943</v>
       </c>
@@ -31834,7 +31888,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="321" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
         <v>943</v>
       </c>
@@ -31917,7 +31971,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="322" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
         <v>943</v>
       </c>
@@ -32000,7 +32054,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="323" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>943</v>
       </c>
@@ -32083,7 +32137,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="324" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
         <v>943</v>
       </c>
@@ -32166,7 +32220,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="325" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>943</v>
       </c>
@@ -32249,7 +32303,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="326" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
         <v>943</v>
       </c>
@@ -32320,7 +32374,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="327" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
         <v>943</v>
       </c>
@@ -32391,7 +32445,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="328" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
         <v>943</v>
       </c>
@@ -32462,7 +32516,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="329" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
         <v>943</v>
       </c>
@@ -32533,7 +32587,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="330" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
         <v>943</v>
       </c>
@@ -32618,7 +32672,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="331" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>943</v>
       </c>
@@ -32703,7 +32757,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="332" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="3" t="s">
         <v>943</v>
       </c>
@@ -32788,7 +32842,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="333" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>943</v>
       </c>
@@ -32873,7 +32927,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="334" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
         <v>943</v>
       </c>
@@ -32958,7 +33012,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="335" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>943</v>
       </c>
@@ -33029,7 +33083,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="336" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
         <v>943</v>
       </c>
@@ -33100,7 +33154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="337" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
         <v>943</v>
       </c>
@@ -33175,7 +33229,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="338" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>943</v>
       </c>
@@ -33246,7 +33300,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="339" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33311,7 +33365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33376,7 +33430,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33441,7 +33495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="342" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33506,7 +33560,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="343" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33571,7 +33625,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33636,7 +33690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="345" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33701,7 +33755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="346" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33766,7 +33820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="347" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33831,7 +33885,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="348" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33896,7 +33950,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="349" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33961,7 +34015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34026,7 +34080,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="351" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34091,7 +34145,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="352" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34156,7 +34210,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="353" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34221,7 +34275,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="354" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34286,7 +34340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="355" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34351,7 +34405,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="356" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34416,7 +34470,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="357" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34481,7 +34535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="358" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34546,7 +34600,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="359" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="3" t="s">
         <v>1417</v>
       </c>
@@ -34611,7 +34665,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="360" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34676,7 +34730,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="361" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3" t="s">
         <v>1417</v>
       </c>
@@ -34741,7 +34795,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="362" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34806,7 +34860,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="363" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3" t="s">
         <v>1417</v>
       </c>
@@ -34871,7 +34925,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="364" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34936,7 +34990,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="365" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35001,7 +35055,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="366" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35066,7 +35120,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="367" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35131,7 +35185,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="368" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35196,7 +35250,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="369" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35261,7 +35315,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="370" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35326,7 +35380,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="371" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35391,7 +35445,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="372" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35456,7 +35510,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="373" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35521,7 +35575,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="374" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>1479</v>
       </c>
@@ -35598,7 +35652,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="375" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
         <v>1479</v>
       </c>
@@ -35675,7 +35729,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="376" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
         <v>1479</v>
       </c>
@@ -35752,7 +35806,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="377" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="3" t="s">
         <v>1479</v>
       </c>
@@ -35833,7 +35887,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="378" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
         <v>1479</v>
       </c>
@@ -35914,7 +35968,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="379" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="3" t="s">
         <v>1479</v>
       </c>
@@ -35995,7 +36049,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="380" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36076,7 +36130,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="381" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36157,7 +36211,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="382" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36238,7 +36292,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="383" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36319,7 +36373,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="384" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36394,7 +36448,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="385" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36469,7 +36523,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="386" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36550,7 +36604,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="387" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36631,7 +36685,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="388" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36712,7 +36766,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="389" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36799,7 +36853,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="390" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36886,7 +36940,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="391" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36973,7 +37027,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="392" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37060,7 +37114,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="393" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37135,7 +37189,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="394" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37210,7 +37264,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="395" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37285,7 +37339,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="396" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37356,7 +37410,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="397" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37427,7 +37481,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="398" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37498,7 +37552,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="399" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37579,7 +37633,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="400" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37660,7 +37714,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="401" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37741,7 +37795,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="402" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37822,7 +37876,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="403" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37903,7 +37957,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="404" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37984,7 +38038,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="405" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38059,7 +38113,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="406" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38134,7 +38188,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="407" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38205,7 +38259,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="408" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38276,7 +38330,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="409" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38347,7 +38401,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="410" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38430,7 +38484,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="411" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38513,7 +38567,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="412" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38588,7 +38642,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="413" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38663,7 +38717,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="414" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38738,7 +38792,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="415" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38825,7 +38879,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="416" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38912,7 +38966,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="417" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38999,7 +39053,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="418" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39080,7 +39134,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="419" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39161,7 +39215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="420" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39242,7 +39296,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="421" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39323,7 +39377,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="422" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39404,7 +39458,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="423" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39485,7 +39539,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="424" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39566,7 +39620,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="425" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39641,7 +39695,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="426" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39716,7 +39770,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="427" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39791,7 +39845,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="428" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39866,7 +39920,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="429" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39941,7 +39995,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="430" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40016,7 +40070,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="431" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40103,7 +40157,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="432" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40178,7 +40232,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="433" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40249,7 +40303,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="434" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40320,7 +40374,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="435" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40391,7 +40445,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="436" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40466,7 +40520,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="437" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40541,7 +40595,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="438" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40622,7 +40676,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="439" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40701,7 +40755,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="440" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40780,7 +40834,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="441" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40859,7 +40913,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="442" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40938,7 +40992,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="443" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41017,7 +41071,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="444" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41096,7 +41150,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="445" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41175,7 +41229,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="446" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41258,7 +41312,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="447" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41341,7 +41395,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="448" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41424,7 +41478,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="449" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41507,7 +41561,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="450" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41590,7 +41644,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="451" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41673,7 +41727,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="452" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41756,7 +41810,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="453" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41839,7 +41893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="454" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41926,7 +41980,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="455" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42013,7 +42067,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="456" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42100,7 +42154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="457" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42187,7 +42241,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="458" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42274,7 +42328,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="459" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42353,7 +42407,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="460" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42432,7 +42486,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="461" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42511,7 +42565,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="462" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42590,7 +42644,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="463" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42669,7 +42723,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="464" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42748,7 +42802,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="465" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42827,7 +42881,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="466" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42916,7 +42970,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="467" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43005,7 +43059,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="468" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43094,7 +43148,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="469" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43183,7 +43237,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="470" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43272,7 +43326,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="471" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43361,7 +43415,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="472" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43450,7 +43504,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="473" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43539,7 +43593,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="474" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43628,7 +43682,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="475" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43717,7 +43771,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="476" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43794,7 +43848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="477" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43865,7 +43919,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="478" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43938,7 +43992,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="479" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44015,7 +44069,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="480" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44102,7 +44156,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="481" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44181,7 +44235,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="482" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44255,7 +44309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="483" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44342,7 +44396,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="484" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44429,7 +44483,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="485" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44506,7 +44560,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="486" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44593,7 +44647,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="487" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44670,7 +44724,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="488" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44749,7 +44803,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="489" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44830,7 +44884,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="490" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44907,7 +44961,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="491" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44982,7 +45036,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="492" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45062,7 +45116,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="493" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45143,7 +45197,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="494" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45220,7 +45274,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="495" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45297,7 +45351,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="496" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45372,7 +45426,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="497" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45447,7 +45501,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="498" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45524,7 +45578,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="499" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45599,7 +45653,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="500" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45680,7 +45734,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="501" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45761,7 +45815,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="502" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45838,7 +45892,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="503" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45915,7 +45969,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="504" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46000,7 +46054,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="505" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46085,7 +46139,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="506" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46170,7 +46224,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="507" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46255,7 +46309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="508" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46340,7 +46394,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="509" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46425,7 +46479,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="510" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46510,7 +46564,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="511" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46595,7 +46649,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="512" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46680,7 +46734,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="513" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46765,7 +46819,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="514" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46850,7 +46904,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="515" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46931,7 +46985,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="516" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47012,7 +47066,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="517" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="3" t="s">
         <v>1479</v>
       </c>
@@ -47099,7 +47153,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="518" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47186,7 +47240,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="519" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="3" t="s">
         <v>1479</v>
       </c>
@@ -47269,7 +47323,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="520" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47352,7 +47406,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="521" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="3" t="s">
         <v>1479</v>
       </c>
@@ -47433,7 +47487,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="522" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47520,7 +47574,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="523" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47607,7 +47661,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="524" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="3" t="s">
         <v>2023</v>
       </c>
@@ -47684,7 +47738,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="525" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="2" t="s">
         <v>2023</v>
       </c>
@@ -47765,7 +47819,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="526" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="3" t="s">
         <v>2023</v>
       </c>
@@ -47846,7 +47900,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="527" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="2" t="s">
         <v>2023</v>
       </c>
@@ -47927,7 +47981,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="528" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48008,7 +48062,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="529" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48089,7 +48143,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="530" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48170,7 +48224,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="531" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48245,7 +48299,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="532" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48326,7 +48380,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="533" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48413,7 +48467,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="534" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48500,7 +48554,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="535" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48587,7 +48641,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="536" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48674,7 +48728,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="537" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48757,7 +48811,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="538" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48840,7 +48894,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="539" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48923,7 +48977,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="540" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49006,7 +49060,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="541" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49089,7 +49143,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="542" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49172,7 +49226,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="543" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49255,7 +49309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="544" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49338,7 +49392,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="545" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49423,7 +49477,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="546" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49508,7 +49562,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="547" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49593,7 +49647,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="548" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49664,7 +49718,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="549" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49751,7 +49805,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="550" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49838,7 +49892,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="551" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49913,7 +49967,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="552" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49988,7 +50042,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="553" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50063,7 +50117,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="554" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50150,7 +50204,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="555" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50225,7 +50279,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="556" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50300,7 +50354,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="557" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50371,7 +50425,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="558" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50442,7 +50496,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="559" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50529,7 +50583,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="560" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50616,7 +50670,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="561" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50697,7 +50751,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="562" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50778,7 +50832,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="563" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50863,7 +50917,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="564" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50948,7 +51002,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="565" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51029,7 +51083,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="566" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51118,7 +51172,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="567" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51207,7 +51261,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="568" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51296,7 +51350,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="569" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51385,7 +51439,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="570" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51474,7 +51528,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="571" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51559,7 +51613,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="572" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51644,7 +51698,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="573" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51729,7 +51783,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="574" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51816,7 +51870,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="575" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51903,7 +51957,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="576" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51990,7 +52044,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="577" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52073,7 +52127,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="578" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52152,7 +52206,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="579" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52226,7 +52280,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="580" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52298,7 +52352,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="581" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52372,7 +52426,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="582" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52457,7 +52511,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="583" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52538,7 +52592,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="584" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52619,7 +52673,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="585" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52700,7 +52754,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="586" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52775,7 +52829,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="587" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52850,7 +52904,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="588" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52937,7 +52991,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="589" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="2" t="s">
         <v>2023</v>
       </c>
@@ -53024,7 +53078,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="590" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="8" t="s">
         <v>292</v>
       </c>
@@ -53099,24 +53153,313 @@
         <v>43</v>
       </c>
     </row>
-    <row r="591" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="591" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A591" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B591" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C591" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D591" s="10" t="s">
+        <v>2444</v>
+      </c>
+      <c r="E591" s="8" t="s">
+        <v>2445</v>
+      </c>
+      <c r="H591" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I591" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J591" s="2" t="s">
+        <v>2197</v>
+      </c>
+      <c r="K591" s="2"/>
+      <c r="L591" s="2"/>
+      <c r="M591" s="2" t="s">
+        <v>2313</v>
+      </c>
+      <c r="N591" s="2"/>
+      <c r="O591" s="2"/>
+      <c r="P591" s="2" t="s">
+        <v>2281</v>
+      </c>
+      <c r="Q591" s="2" t="s">
+        <v>2291</v>
+      </c>
+      <c r="R591" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="S591" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T591" s="2" t="s">
+        <v>2392</v>
+      </c>
+      <c r="U591" s="2" t="s">
+        <v>2429</v>
+      </c>
+      <c r="V591" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W591" s="3"/>
+      <c r="X591" s="3"/>
+      <c r="Y591" s="7"/>
+      <c r="Z591" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AA591" t="s">
+        <v>2437</v>
+      </c>
+      <c r="AB591" t="s">
+        <v>2439</v>
+      </c>
+      <c r="AC591" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD591" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE591" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="592" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A592" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="B592" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="C592" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="D592" s="10" t="s">
+        <v>2446</v>
+      </c>
+      <c r="E592" s="8" t="s">
+        <v>2447</v>
+      </c>
+      <c r="H592" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="I592" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="J592" s="2"/>
+      <c r="K592" s="2"/>
+      <c r="L592" s="2"/>
+      <c r="M592" s="2" t="s">
+        <v>2452</v>
+      </c>
+      <c r="N592" s="2"/>
+      <c r="O592" s="2"/>
+      <c r="P592" s="2" t="s">
+        <v>2284</v>
+      </c>
+      <c r="Q592" s="2" t="s">
+        <v>2293</v>
+      </c>
+      <c r="R592" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="S592" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="T592" s="2"/>
+      <c r="U592" s="2"/>
+      <c r="V592" s="2"/>
+      <c r="W592" s="3"/>
+      <c r="X592" s="3"/>
+      <c r="Y592" s="7"/>
+      <c r="Z592" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AA592" t="s">
+        <v>2437</v>
+      </c>
+      <c r="AB592" t="s">
+        <v>2439</v>
+      </c>
+      <c r="AC592" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="AD592" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="AE592" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="593" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A593" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="B593" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="C593" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="D593" s="11" t="s">
+        <v>2448</v>
+      </c>
+      <c r="E593" s="8" t="s">
+        <v>2449</v>
+      </c>
+      <c r="H593" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="I593" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="J593" s="2" t="s">
+        <v>2224</v>
+      </c>
+      <c r="K593" s="2"/>
+      <c r="L593" s="2"/>
+      <c r="M593" s="2" t="s">
+        <v>2335</v>
+      </c>
+      <c r="N593" s="2"/>
+      <c r="O593" s="2"/>
+      <c r="P593" s="2" t="s">
+        <v>2285</v>
+      </c>
+      <c r="Q593" s="2" t="s">
+        <v>2294</v>
+      </c>
+      <c r="R593" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="S593" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="T593" s="2"/>
+      <c r="U593" s="2"/>
+      <c r="V593" s="2"/>
+      <c r="W593" s="2"/>
+      <c r="X593" s="2"/>
+      <c r="Y593" s="5"/>
+      <c r="Z593" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AA593" t="s">
+        <v>2437</v>
+      </c>
+      <c r="AB593" t="s">
+        <v>2439</v>
+      </c>
+      <c r="AC593" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="AD593" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="AE593" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="594" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A594" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B594" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="C594" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D594" s="10" t="s">
+        <v>2450</v>
+      </c>
+      <c r="E594" s="8" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F594" s="8" t="s">
+        <v>2451</v>
+      </c>
+      <c r="H594" s="3" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I594" s="3" t="s">
+        <v>1953</v>
+      </c>
+      <c r="J594" s="2" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K594" s="2" t="s">
+        <v>2303</v>
+      </c>
+      <c r="L594" s="2"/>
+      <c r="M594" s="2" t="s">
+        <v>2369</v>
+      </c>
+      <c r="N594" s="2" t="s">
+        <v>2389</v>
+      </c>
+      <c r="O594" s="2"/>
+      <c r="P594" s="2"/>
+      <c r="Q594" s="2"/>
+      <c r="R594" s="3" t="s">
+        <v>1905</v>
+      </c>
+      <c r="S594" s="2"/>
+      <c r="T594" t="s">
+        <v>2422</v>
+      </c>
+      <c r="U594" s="2" t="s">
+        <v>2433</v>
+      </c>
+      <c r="V594" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="W594" t="s">
+        <v>2434</v>
+      </c>
+      <c r="X594" t="s">
+        <v>2435</v>
+      </c>
+      <c r="Y594" t="s">
+        <v>2441</v>
+      </c>
+      <c r="Z594" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AA594" t="s">
+        <v>2437</v>
+      </c>
+      <c r="AB594" t="s">
+        <v>2439</v>
+      </c>
+      <c r="AC594" s="3" t="s">
+        <v>1953</v>
+      </c>
+      <c r="AD594" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="AE594" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="595" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="596" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="597" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="598" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="599" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="600" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="601" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="602" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="603" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="604" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="605" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="606" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="607" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="608" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="609" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="610" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="611" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -53140,7 +53483,14 @@
     <row r="629" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="630" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:AE590" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AE594" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="MANGALORE"/>
+        <filter val="UDIPI"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/CFA-Stockist-HQ_Mapping_Master_Updated.xlsx
+++ b/CFA-Stockist-HQ_Mapping_Master_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milind\Desktop\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2024B0-A2E4-417E-B38D-D780116DDE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D102F88F-8C88-4F92-A56D-FEE38FEF4491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12972" uniqueCount="2453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13028" uniqueCount="2458">
   <si>
     <t>Distributor Code</t>
   </si>
@@ -7394,7 +7394,22 @@
     <t>DHARMADAS MEDICAL</t>
   </si>
   <si>
-    <t>Vacant Bangalore</t>
+    <t>ADLA101</t>
+  </si>
+  <si>
+    <t>Hithesh K. R.</t>
+  </si>
+  <si>
+    <t>ADLA20</t>
+  </si>
+  <si>
+    <t>SOUGATA MUKHERJEE</t>
+  </si>
+  <si>
+    <t>ADLA85</t>
+  </si>
+  <si>
+    <t>RAMESH KUMAR TIWARI</t>
   </si>
 </sst>
 </file>
@@ -7877,7 +7892,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE630"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -8005,7 +8019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -8070,7 +8084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -8135,7 +8149,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -8200,7 +8214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -8269,7 +8283,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
@@ -8338,7 +8352,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
@@ -8407,7 +8421,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -8476,7 +8490,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
@@ -8545,7 +8559,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -8626,7 +8640,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>32</v>
       </c>
@@ -8707,7 +8721,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -8788,7 +8802,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>32</v>
       </c>
@@ -8869,7 +8883,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -8950,7 +8964,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
@@ -9031,7 +9045,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -9112,7 +9126,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -9193,7 +9207,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -9274,7 +9288,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -9355,7 +9369,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
@@ -9436,7 +9450,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
@@ -9521,7 +9535,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -9606,7 +9620,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>32</v>
       </c>
@@ -9691,7 +9705,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -9776,7 +9790,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>32</v>
       </c>
@@ -9861,7 +9875,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>32</v>
       </c>
@@ -9946,7 +9960,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
@@ -10027,7 +10041,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
@@ -10108,7 +10122,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
@@ -10189,7 +10203,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -10270,7 +10284,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
@@ -10351,7 +10365,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -10432,7 +10446,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
@@ -10513,7 +10527,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -10590,7 +10604,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
@@ -10667,7 +10681,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -10744,7 +10758,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>32</v>
       </c>
@@ -10821,7 +10835,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
@@ -10902,7 +10916,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>32</v>
       </c>
@@ -10981,7 +10995,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
@@ -11062,7 +11076,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
@@ -11137,7 +11151,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>32</v>
       </c>
@@ -11218,7 +11232,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>32</v>
       </c>
@@ -11299,7 +11313,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>32</v>
       </c>
@@ -11380,7 +11394,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>32</v>
       </c>
@@ -11461,7 +11475,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>32</v>
       </c>
@@ -11489,10 +11503,14 @@
       <c r="I46" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="J46" s="2"/>
+      <c r="J46" t="s">
+        <v>2456</v>
+      </c>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
+      <c r="M46" t="s">
+        <v>2457</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2" t="s">
@@ -11538,7 +11556,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>32</v>
       </c>
@@ -11619,7 +11637,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>204</v>
       </c>
@@ -11690,7 +11708,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>204</v>
       </c>
@@ -11761,7 +11779,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>204</v>
       </c>
@@ -11832,7 +11850,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>204</v>
       </c>
@@ -11907,7 +11925,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>204</v>
       </c>
@@ -11982,7 +12000,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>204</v>
       </c>
@@ -12057,7 +12075,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>204</v>
       </c>
@@ -12132,7 +12150,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>204</v>
       </c>
@@ -12207,7 +12225,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>204</v>
       </c>
@@ -12282,7 +12300,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>204</v>
       </c>
@@ -12353,7 +12371,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>204</v>
       </c>
@@ -12424,7 +12442,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>204</v>
       </c>
@@ -12499,7 +12517,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>204</v>
       </c>
@@ -12574,7 +12592,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>204</v>
       </c>
@@ -12649,7 +12667,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="62" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>204</v>
       </c>
@@ -12724,7 +12742,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="63" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>204</v>
       </c>
@@ -12799,7 +12817,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>204</v>
       </c>
@@ -12870,7 +12888,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>204</v>
       </c>
@@ -12941,7 +12959,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>204</v>
       </c>
@@ -13016,7 +13034,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>204</v>
       </c>
@@ -13091,7 +13109,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>204</v>
       </c>
@@ -13166,7 +13184,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>292</v>
       </c>
@@ -13247,7 +13265,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>292</v>
       </c>
@@ -13328,7 +13346,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>292</v>
       </c>
@@ -13409,7 +13427,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>292</v>
       </c>
@@ -13490,7 +13508,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>292</v>
       </c>
@@ -13571,7 +13589,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>292</v>
       </c>
@@ -13652,7 +13670,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>292</v>
       </c>
@@ -13727,7 +13745,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>292</v>
       </c>
@@ -13802,7 +13820,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>292</v>
       </c>
@@ -13877,7 +13895,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>292</v>
       </c>
@@ -13952,7 +13970,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>292</v>
       </c>
@@ -14027,7 +14045,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>292</v>
       </c>
@@ -14102,7 +14120,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>292</v>
       </c>
@@ -14177,7 +14195,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>292</v>
       </c>
@@ -14252,7 +14270,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>292</v>
       </c>
@@ -14327,7 +14345,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>292</v>
       </c>
@@ -14402,7 +14420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>292</v>
       </c>
@@ -14477,7 +14495,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>292</v>
       </c>
@@ -14552,7 +14570,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>292</v>
       </c>
@@ -14627,7 +14645,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>292</v>
       </c>
@@ -14702,7 +14720,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>292</v>
       </c>
@@ -14777,7 +14795,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>292</v>
       </c>
@@ -14852,7 +14870,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="91" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>292</v>
       </c>
@@ -14927,7 +14945,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>292</v>
       </c>
@@ -14998,7 +15016,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="93" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>292</v>
       </c>
@@ -15069,7 +15087,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="94" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>292</v>
       </c>
@@ -15140,7 +15158,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>292</v>
       </c>
@@ -15211,7 +15229,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>292</v>
       </c>
@@ -15282,7 +15300,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>292</v>
       </c>
@@ -15363,7 +15381,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>292</v>
       </c>
@@ -15444,7 +15462,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>292</v>
       </c>
@@ -15525,7 +15543,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>292</v>
       </c>
@@ -15606,7 +15624,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>292</v>
       </c>
@@ -15687,7 +15705,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>292</v>
       </c>
@@ -15768,7 +15786,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="103" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>292</v>
       </c>
@@ -15843,7 +15861,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>292</v>
       </c>
@@ -15918,7 +15936,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="105" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>292</v>
       </c>
@@ -15993,7 +16011,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>292</v>
       </c>
@@ -16068,7 +16086,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="107" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>292</v>
       </c>
@@ -16143,7 +16161,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="108" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>292</v>
       </c>
@@ -16218,7 +16236,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>292</v>
       </c>
@@ -16293,7 +16311,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -16368,7 +16386,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>292</v>
       </c>
@@ -16443,7 +16461,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>292</v>
       </c>
@@ -16518,7 +16536,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>292</v>
       </c>
@@ -16593,7 +16611,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>292</v>
       </c>
@@ -16668,7 +16686,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>292</v>
       </c>
@@ -16743,7 +16761,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>292</v>
       </c>
@@ -16818,7 +16836,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>292</v>
       </c>
@@ -16893,7 +16911,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="118" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>292</v>
       </c>
@@ -16974,7 +16992,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="119" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>292</v>
       </c>
@@ -17055,7 +17073,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>292</v>
       </c>
@@ -17136,7 +17154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>292</v>
       </c>
@@ -17207,7 +17225,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>487</v>
       </c>
@@ -17286,7 +17304,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="123" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>487</v>
       </c>
@@ -17357,7 +17375,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="124" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>487</v>
       </c>
@@ -17428,7 +17446,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="125" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>487</v>
       </c>
@@ -17499,7 +17517,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="126" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>487</v>
       </c>
@@ -17602,11 +17620,13 @@
       <c r="I127" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="J127" s="2"/>
+      <c r="J127" t="s">
+        <v>2452</v>
+      </c>
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
-      <c r="M127" s="2" t="s">
-        <v>2452</v>
+      <c r="M127" t="s">
+        <v>2453</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17675,11 +17695,13 @@
       <c r="I128" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="J128" s="2"/>
+      <c r="J128" t="s">
+        <v>2452</v>
+      </c>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
-      <c r="M128" s="2" t="s">
-        <v>2452</v>
+      <c r="M128" t="s">
+        <v>2453</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17748,11 +17770,13 @@
       <c r="I129" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="J129" s="2"/>
+      <c r="J129" t="s">
+        <v>2452</v>
+      </c>
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
-      <c r="M129" s="2" t="s">
-        <v>2452</v>
+      <c r="M129" t="s">
+        <v>2453</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17793,7 +17817,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>487</v>
       </c>
@@ -17868,7 +17892,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>487</v>
       </c>
@@ -17943,7 +17967,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>487</v>
       </c>
@@ -18018,7 +18042,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>487</v>
       </c>
@@ -18093,7 +18117,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="134" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>487</v>
       </c>
@@ -18168,7 +18192,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>487</v>
       </c>
@@ -18243,7 +18267,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>487</v>
       </c>
@@ -18318,7 +18342,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="137" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>487</v>
       </c>
@@ -18417,11 +18441,13 @@
       <c r="I138" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="J138" s="2"/>
+      <c r="J138" t="s">
+        <v>2452</v>
+      </c>
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
-      <c r="M138" s="2" t="s">
-        <v>2452</v>
+      <c r="M138" t="s">
+        <v>2453</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -18490,11 +18516,13 @@
       <c r="I139" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="J139" s="2"/>
+      <c r="J139" t="s">
+        <v>2452</v>
+      </c>
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
-      <c r="M139" s="2" t="s">
-        <v>2452</v>
+      <c r="M139" t="s">
+        <v>2453</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18535,7 +18563,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>487</v>
       </c>
@@ -18600,7 +18628,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>487</v>
       </c>
@@ -18665,7 +18693,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>487</v>
       </c>
@@ -18746,7 +18774,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>487</v>
       </c>
@@ -18827,7 +18855,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>487</v>
       </c>
@@ -18908,7 +18936,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>487</v>
       </c>
@@ -18989,7 +19017,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>594</v>
       </c>
@@ -19058,7 +19086,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>594</v>
       </c>
@@ -19127,7 +19155,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>594</v>
       </c>
@@ -19196,7 +19224,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>594</v>
       </c>
@@ -19265,7 +19293,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>594</v>
       </c>
@@ -19340,7 +19368,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
         <v>594</v>
       </c>
@@ -19415,7 +19443,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>594</v>
       </c>
@@ -19480,7 +19508,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>594</v>
       </c>
@@ -19555,7 +19583,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>594</v>
       </c>
@@ -19630,7 +19658,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
         <v>594</v>
       </c>
@@ -19695,7 +19723,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>594</v>
       </c>
@@ -19770,7 +19798,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
         <v>594</v>
       </c>
@@ -19845,7 +19873,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>594</v>
       </c>
@@ -19920,7 +19948,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
         <v>653</v>
       </c>
@@ -20001,7 +20029,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>653</v>
       </c>
@@ -20082,7 +20110,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="161" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
         <v>653</v>
       </c>
@@ -20163,7 +20191,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="162" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>653</v>
       </c>
@@ -20244,7 +20272,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="163" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>653</v>
       </c>
@@ -20325,7 +20353,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="164" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>653</v>
       </c>
@@ -20396,7 +20424,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
         <v>653</v>
       </c>
@@ -20467,7 +20495,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="166" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>653</v>
       </c>
@@ -20548,7 +20576,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="167" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>653</v>
       </c>
@@ -20623,7 +20651,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="168" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>653</v>
       </c>
@@ -20698,7 +20726,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="169" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
         <v>653</v>
       </c>
@@ -20773,7 +20801,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="170" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>653</v>
       </c>
@@ -20848,7 +20876,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>653</v>
       </c>
@@ -20923,7 +20951,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="172" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>653</v>
       </c>
@@ -20998,7 +21026,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="173" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
         <v>653</v>
       </c>
@@ -21069,7 +21097,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="174" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>653</v>
       </c>
@@ -21140,7 +21168,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
         <v>653</v>
       </c>
@@ -21211,7 +21239,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>653</v>
       </c>
@@ -21282,7 +21310,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
         <v>653</v>
       </c>
@@ -21353,7 +21381,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="178" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>653</v>
       </c>
@@ -21424,7 +21452,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="179" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
         <v>653</v>
       </c>
@@ -21495,7 +21523,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="180" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>653</v>
       </c>
@@ -21566,7 +21594,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="181" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
         <v>653</v>
       </c>
@@ -21637,7 +21665,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="182" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>653</v>
       </c>
@@ -21708,7 +21736,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="183" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>653</v>
       </c>
@@ -21779,7 +21807,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="184" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>653</v>
       </c>
@@ -21850,7 +21878,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="185" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
         <v>653</v>
       </c>
@@ -21921,7 +21949,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="186" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>653</v>
       </c>
@@ -21996,7 +22024,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="187" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
         <v>653</v>
       </c>
@@ -22071,7 +22099,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="188" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>653</v>
       </c>
@@ -22146,7 +22174,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="189" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
         <v>653</v>
       </c>
@@ -22221,7 +22249,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="190" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>653</v>
       </c>
@@ -22294,7 +22322,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="191" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
         <v>653</v>
       </c>
@@ -22369,7 +22397,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="192" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>653</v>
       </c>
@@ -22450,7 +22478,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="193" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
         <v>653</v>
       </c>
@@ -22531,7 +22559,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="194" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>653</v>
       </c>
@@ -22612,7 +22640,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="195" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
         <v>653</v>
       </c>
@@ -22693,7 +22721,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="196" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>653</v>
       </c>
@@ -22768,7 +22796,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="197" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
         <v>653</v>
       </c>
@@ -22839,7 +22867,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="198" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>653</v>
       </c>
@@ -22910,7 +22938,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
         <v>653</v>
       </c>
@@ -22985,7 +23013,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="200" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
         <v>653</v>
       </c>
@@ -23060,7 +23088,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="201" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>653</v>
       </c>
@@ -23135,7 +23163,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="202" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
         <v>653</v>
       </c>
@@ -23216,7 +23244,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="203" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>653</v>
       </c>
@@ -23291,7 +23319,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="204" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
         <v>653</v>
       </c>
@@ -23366,7 +23394,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="205" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>826</v>
       </c>
@@ -23431,7 +23459,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="206" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
         <v>826</v>
       </c>
@@ -23500,7 +23528,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="207" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>826</v>
       </c>
@@ -23569,7 +23597,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="208" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
         <v>826</v>
       </c>
@@ -23638,7 +23666,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="209" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>826</v>
       </c>
@@ -23703,7 +23731,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="210" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
         <v>826</v>
       </c>
@@ -23768,7 +23796,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="211" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>826</v>
       </c>
@@ -23833,7 +23861,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="212" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
         <v>826</v>
       </c>
@@ -23902,7 +23930,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="213" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>826</v>
       </c>
@@ -23971,7 +23999,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="214" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
         <v>826</v>
       </c>
@@ -24040,7 +24068,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="215" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>826</v>
       </c>
@@ -24105,7 +24133,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="216" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
         <v>826</v>
       </c>
@@ -24170,7 +24198,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="217" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>826</v>
       </c>
@@ -24233,7 +24261,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="218" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
         <v>826</v>
       </c>
@@ -24298,7 +24326,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="219" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>826</v>
       </c>
@@ -24367,7 +24395,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="220" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
         <v>826</v>
       </c>
@@ -24436,7 +24464,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="221" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>826</v>
       </c>
@@ -24505,7 +24533,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="222" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3" t="s">
         <v>826</v>
       </c>
@@ -24574,7 +24602,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="223" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>826</v>
       </c>
@@ -24643,7 +24671,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="224" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
         <v>826</v>
       </c>
@@ -24708,7 +24736,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="225" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>826</v>
       </c>
@@ -24773,7 +24801,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="226" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
         <v>826</v>
       </c>
@@ -24838,7 +24866,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="227" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>826</v>
       </c>
@@ -24903,7 +24931,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="228" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
         <v>826</v>
       </c>
@@ -24968,7 +24996,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="229" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>826</v>
       </c>
@@ -25033,7 +25061,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="230" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>826</v>
       </c>
@@ -25098,7 +25126,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="231" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>826</v>
       </c>
@@ -25163,7 +25191,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="232" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
         <v>826</v>
       </c>
@@ -25228,7 +25256,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="233" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>943</v>
       </c>
@@ -25303,7 +25331,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="234" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
         <v>943</v>
       </c>
@@ -25378,7 +25406,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="235" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>943</v>
       </c>
@@ -25453,7 +25481,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="236" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
         <v>943</v>
       </c>
@@ -25528,7 +25556,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="237" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>943</v>
       </c>
@@ -25603,7 +25631,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="238" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
         <v>943</v>
       </c>
@@ -25678,7 +25706,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="239" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>943</v>
       </c>
@@ -25753,7 +25781,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="240" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
         <v>943</v>
       </c>
@@ -25828,7 +25856,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>943</v>
       </c>
@@ -25899,7 +25927,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="242" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
         <v>943</v>
       </c>
@@ -25970,7 +25998,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="243" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>943</v>
       </c>
@@ -26041,7 +26069,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="244" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
         <v>943</v>
       </c>
@@ -26112,7 +26140,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="245" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>943</v>
       </c>
@@ -26187,7 +26215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="246" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
         <v>943</v>
       </c>
@@ -26262,7 +26290,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="247" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>943</v>
       </c>
@@ -26337,7 +26365,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="248" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
         <v>943</v>
       </c>
@@ -26412,7 +26440,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="249" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>943</v>
       </c>
@@ -26487,7 +26515,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="250" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
         <v>943</v>
       </c>
@@ -26568,7 +26596,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="251" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>943</v>
       </c>
@@ -26649,7 +26677,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="252" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
         <v>943</v>
       </c>
@@ -26724,7 +26752,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="253" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>943</v>
       </c>
@@ -26799,7 +26827,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="254" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
         <v>943</v>
       </c>
@@ -26874,7 +26902,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="255" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>943</v>
       </c>
@@ -26949,7 +26977,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="256" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
         <v>943</v>
       </c>
@@ -27024,7 +27052,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="257" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>943</v>
       </c>
@@ -27099,7 +27127,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="258" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
         <v>943</v>
       </c>
@@ -27174,7 +27202,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="259" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>943</v>
       </c>
@@ -27249,7 +27277,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="260" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
         <v>943</v>
       </c>
@@ -27324,7 +27352,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="261" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>943</v>
       </c>
@@ -27399,7 +27427,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="262" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
         <v>943</v>
       </c>
@@ -27474,7 +27502,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="263" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>943</v>
       </c>
@@ -27549,7 +27577,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="264" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
         <v>943</v>
       </c>
@@ -27620,7 +27648,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="265" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>943</v>
       </c>
@@ -27691,7 +27719,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="266" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
         <v>943</v>
       </c>
@@ -27772,7 +27800,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="267" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>943</v>
       </c>
@@ -27853,7 +27881,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="268" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
         <v>943</v>
       </c>
@@ -27934,7 +27962,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="269" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>943</v>
       </c>
@@ -28015,7 +28043,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="270" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
         <v>943</v>
       </c>
@@ -28090,7 +28118,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="271" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>943</v>
       </c>
@@ -28165,7 +28193,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="272" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
         <v>943</v>
       </c>
@@ -28240,7 +28268,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="273" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>943</v>
       </c>
@@ -28315,7 +28343,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="274" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
         <v>943</v>
       </c>
@@ -28390,7 +28418,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="275" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>943</v>
       </c>
@@ -28473,7 +28501,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="276" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
         <v>943</v>
       </c>
@@ -28556,7 +28584,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="277" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>943</v>
       </c>
@@ -28639,7 +28667,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="278" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
         <v>943</v>
       </c>
@@ -28714,7 +28742,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="279" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>943</v>
       </c>
@@ -28789,7 +28817,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="280" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
         <v>943</v>
       </c>
@@ -28864,7 +28892,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="281" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>943</v>
       </c>
@@ -28939,7 +28967,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="282" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
         <v>943</v>
       </c>
@@ -29014,7 +29042,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="283" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>943</v>
       </c>
@@ -29089,7 +29117,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="284" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
         <v>943</v>
       </c>
@@ -29164,7 +29192,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="285" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>943</v>
       </c>
@@ -29239,7 +29267,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="286" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
         <v>943</v>
       </c>
@@ -29314,7 +29342,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="287" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>943</v>
       </c>
@@ -29389,7 +29417,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="288" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
         <v>943</v>
       </c>
@@ -29464,7 +29492,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="289" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>943</v>
       </c>
@@ -29539,7 +29567,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="290" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
         <v>943</v>
       </c>
@@ -29614,7 +29642,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="291" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>943</v>
       </c>
@@ -29689,7 +29717,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="292" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
         <v>943</v>
       </c>
@@ -29764,7 +29792,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="293" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>943</v>
       </c>
@@ -29839,7 +29867,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="294" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
         <v>943</v>
       </c>
@@ -29914,7 +29942,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="295" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>943</v>
       </c>
@@ -29989,7 +30017,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="296" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
         <v>943</v>
       </c>
@@ -30064,7 +30092,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="297" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>943</v>
       </c>
@@ -30139,7 +30167,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="298" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
         <v>943</v>
       </c>
@@ -30214,7 +30242,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="299" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>943</v>
       </c>
@@ -30289,7 +30317,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="300" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
         <v>943</v>
       </c>
@@ -30364,7 +30392,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="301" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>943</v>
       </c>
@@ -30439,7 +30467,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="302" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
         <v>943</v>
       </c>
@@ -30514,7 +30542,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="303" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>943</v>
       </c>
@@ -30589,7 +30617,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="304" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
         <v>943</v>
       </c>
@@ -30664,7 +30692,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="305" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>943</v>
       </c>
@@ -30739,7 +30767,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="306" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
         <v>943</v>
       </c>
@@ -30814,7 +30842,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="307" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>943</v>
       </c>
@@ -30889,7 +30917,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="308" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
         <v>943</v>
       </c>
@@ -30964,7 +30992,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="309" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>943</v>
       </c>
@@ -31039,7 +31067,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="310" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
         <v>943</v>
       </c>
@@ -31114,7 +31142,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="311" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>943</v>
       </c>
@@ -31189,7 +31217,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="312" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
         <v>943</v>
       </c>
@@ -31264,7 +31292,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="313" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>943</v>
       </c>
@@ -31339,7 +31367,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="314" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
         <v>943</v>
       </c>
@@ -31414,7 +31442,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="315" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>943</v>
       </c>
@@ -31489,7 +31517,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="316" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
         <v>943</v>
       </c>
@@ -31564,7 +31592,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="317" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>943</v>
       </c>
@@ -31639,7 +31667,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="318" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
         <v>943</v>
       </c>
@@ -31722,7 +31750,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="319" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>943</v>
       </c>
@@ -31805,7 +31833,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="320" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
         <v>943</v>
       </c>
@@ -31888,7 +31916,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="321" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
         <v>943</v>
       </c>
@@ -31971,7 +31999,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="322" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
         <v>943</v>
       </c>
@@ -32054,7 +32082,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="323" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>943</v>
       </c>
@@ -32137,7 +32165,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="324" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
         <v>943</v>
       </c>
@@ -32220,7 +32248,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="325" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>943</v>
       </c>
@@ -32303,7 +32331,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="326" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
         <v>943</v>
       </c>
@@ -32374,7 +32402,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="327" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
         <v>943</v>
       </c>
@@ -32445,7 +32473,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="328" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
         <v>943</v>
       </c>
@@ -32516,7 +32544,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="329" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
         <v>943</v>
       </c>
@@ -32587,7 +32615,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="330" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
         <v>943</v>
       </c>
@@ -32672,7 +32700,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="331" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>943</v>
       </c>
@@ -32757,7 +32785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="332" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="3" t="s">
         <v>943</v>
       </c>
@@ -32842,7 +32870,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="333" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>943</v>
       </c>
@@ -32927,7 +32955,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="334" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
         <v>943</v>
       </c>
@@ -33012,7 +33040,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="335" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>943</v>
       </c>
@@ -33083,7 +33111,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="336" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
         <v>943</v>
       </c>
@@ -33154,7 +33182,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="337" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
         <v>943</v>
       </c>
@@ -33229,7 +33257,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="338" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>943</v>
       </c>
@@ -33300,7 +33328,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="339" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33365,7 +33393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33430,7 +33458,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33495,7 +33523,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="342" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33560,7 +33588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="343" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33625,7 +33653,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33690,7 +33718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="345" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33755,7 +33783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="346" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33820,7 +33848,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="347" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3" t="s">
         <v>1338</v>
       </c>
@@ -33885,7 +33913,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="348" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>1338</v>
       </c>
@@ -33950,7 +33978,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="349" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34015,7 +34043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34080,7 +34108,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="351" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34145,7 +34173,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="352" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34210,7 +34238,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="353" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34275,7 +34303,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="354" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34340,7 +34368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="355" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34405,7 +34433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="356" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
         <v>1338</v>
       </c>
@@ -34470,7 +34498,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="357" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3" t="s">
         <v>1338</v>
       </c>
@@ -34535,7 +34563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="358" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34600,7 +34628,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="359" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="3" t="s">
         <v>1417</v>
       </c>
@@ -34665,7 +34693,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="360" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34730,7 +34758,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="361" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3" t="s">
         <v>1417</v>
       </c>
@@ -34795,7 +34823,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="362" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34860,7 +34888,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="363" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3" t="s">
         <v>1417</v>
       </c>
@@ -34925,7 +34953,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="364" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>1417</v>
       </c>
@@ -34990,7 +35018,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="365" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35055,7 +35083,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="366" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35120,7 +35148,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="367" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35185,7 +35213,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="368" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35250,7 +35278,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="369" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35315,7 +35343,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="370" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35380,7 +35408,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="371" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35445,7 +35473,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="372" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
         <v>1417</v>
       </c>
@@ -35510,7 +35538,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="373" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3" t="s">
         <v>1417</v>
       </c>
@@ -35575,7 +35603,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="374" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>1479</v>
       </c>
@@ -35652,7 +35680,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="375" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
         <v>1479</v>
       </c>
@@ -35729,7 +35757,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="376" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
         <v>1479</v>
       </c>
@@ -35806,7 +35834,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="377" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="3" t="s">
         <v>1479</v>
       </c>
@@ -35887,7 +35915,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="378" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
         <v>1479</v>
       </c>
@@ -35968,7 +35996,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="379" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36049,7 +36077,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="380" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36130,7 +36158,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="381" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36211,7 +36239,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="382" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36292,7 +36320,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="383" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36373,7 +36401,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="384" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36448,7 +36476,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="385" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36523,7 +36551,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="386" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36604,7 +36632,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="387" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36685,7 +36713,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="388" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36766,7 +36794,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="389" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="3" t="s">
         <v>1479</v>
       </c>
@@ -36853,7 +36881,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="390" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
         <v>1479</v>
       </c>
@@ -36940,7 +36968,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="391" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37027,7 +37055,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="392" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37114,7 +37142,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="393" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37189,7 +37217,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="394" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37264,7 +37292,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="395" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37339,7 +37367,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="396" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37410,7 +37438,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="397" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37481,7 +37509,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="398" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37552,7 +37580,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="399" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37633,7 +37661,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="400" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37714,7 +37742,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="401" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37795,7 +37823,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="402" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
         <v>1479</v>
       </c>
@@ -37876,7 +37904,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="403" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="3" t="s">
         <v>1479</v>
       </c>
@@ -37957,7 +37985,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="404" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38038,7 +38066,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="405" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38113,7 +38141,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="406" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38188,7 +38216,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="407" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38259,7 +38287,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="408" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38330,7 +38358,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="409" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38401,7 +38429,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="410" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38484,7 +38512,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="411" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38567,7 +38595,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="412" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38642,7 +38670,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="413" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38717,7 +38745,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="414" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38792,7 +38820,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="415" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3" t="s">
         <v>1479</v>
       </c>
@@ -38879,7 +38907,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="416" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="2" t="s">
         <v>1479</v>
       </c>
@@ -38966,7 +38994,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="417" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39053,7 +39081,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="418" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39134,7 +39162,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="419" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39215,7 +39243,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="420" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39296,7 +39324,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="421" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39377,7 +39405,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="422" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39458,7 +39486,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="423" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39539,7 +39567,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="424" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39620,7 +39648,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="425" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39695,7 +39723,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="426" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39770,7 +39798,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="427" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39845,7 +39873,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="428" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="2" t="s">
         <v>1479</v>
       </c>
@@ -39920,7 +39948,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="429" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="3" t="s">
         <v>1479</v>
       </c>
@@ -39995,7 +40023,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="430" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40070,7 +40098,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="431" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40157,7 +40185,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="432" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40232,7 +40260,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="433" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40303,7 +40331,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="434" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40374,7 +40402,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="435" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40445,7 +40473,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="436" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40520,7 +40548,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="437" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40595,7 +40623,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="438" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40633,12 +40661,18 @@
       </c>
       <c r="N438" s="2"/>
       <c r="O438" s="2"/>
-      <c r="P438" s="2"/>
-      <c r="Q438" s="2"/>
+      <c r="P438" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q438" t="s">
+        <v>2455</v>
+      </c>
       <c r="R438" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="S438" s="2"/>
+      <c r="S438" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T438" t="s">
         <v>2422</v>
       </c>
@@ -40676,7 +40710,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="439" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40755,7 +40789,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="440" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40834,7 +40868,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="441" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="3" t="s">
         <v>1479</v>
       </c>
@@ -40913,7 +40947,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="442" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="2" t="s">
         <v>1479</v>
       </c>
@@ -40992,7 +41026,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="443" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41071,7 +41105,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="444" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41150,7 +41184,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="445" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41229,7 +41263,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="446" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41312,7 +41346,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="447" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41395,7 +41429,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="448" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41478,7 +41512,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="449" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41561,7 +41595,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="450" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41644,7 +41678,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="451" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41727,7 +41761,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="452" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41810,7 +41844,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="453" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="3" t="s">
         <v>1479</v>
       </c>
@@ -41893,7 +41927,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="454" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="2" t="s">
         <v>1479</v>
       </c>
@@ -41980,7 +42014,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="455" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42067,7 +42101,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="456" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42154,7 +42188,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="457" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42241,7 +42275,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="458" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42328,7 +42362,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="459" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42407,7 +42441,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="460" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42486,7 +42520,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="461" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42565,7 +42599,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="462" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42644,7 +42678,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="463" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42723,7 +42757,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="464" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42802,7 +42836,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="465" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="3" t="s">
         <v>1479</v>
       </c>
@@ -42881,7 +42915,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="466" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="2" t="s">
         <v>1479</v>
       </c>
@@ -42970,7 +43004,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="467" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43059,7 +43093,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="468" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43148,7 +43182,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="469" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43237,7 +43271,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="470" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43326,7 +43360,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="471" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43415,7 +43449,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="472" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43504,7 +43538,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="473" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43593,7 +43627,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="474" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43682,7 +43716,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="475" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43771,7 +43805,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="476" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43848,7 +43882,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="477" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="3" t="s">
         <v>1479</v>
       </c>
@@ -43919,7 +43953,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="478" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="2" t="s">
         <v>1479</v>
       </c>
@@ -43992,7 +44026,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="479" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44069,7 +44103,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="480" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44156,7 +44190,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="481" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44235,7 +44269,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="482" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44309,7 +44343,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="483" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44396,7 +44430,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="484" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44483,7 +44517,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="485" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44560,7 +44594,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="486" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44647,7 +44681,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="487" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44724,7 +44758,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="488" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44803,7 +44837,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="489" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="3" t="s">
         <v>1479</v>
       </c>
@@ -44884,7 +44918,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="490" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="2" t="s">
         <v>1479</v>
       </c>
@@ -44961,7 +44995,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="491" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45036,7 +45070,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="492" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45116,7 +45150,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="493" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45197,7 +45231,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="494" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45274,7 +45308,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="495" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45351,7 +45385,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="496" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45426,7 +45460,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="497" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45501,7 +45535,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="498" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45578,7 +45612,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="499" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45653,7 +45687,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="500" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45734,7 +45768,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="501" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45815,7 +45849,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="502" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="2" t="s">
         <v>1479</v>
       </c>
@@ -45892,7 +45926,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="503" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="3" t="s">
         <v>1479</v>
       </c>
@@ -45969,7 +46003,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="504" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46011,12 +46045,18 @@
         <v>2389</v>
       </c>
       <c r="O504" s="2"/>
-      <c r="P504" s="2"/>
-      <c r="Q504" s="2"/>
+      <c r="P504" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q504" t="s">
+        <v>2455</v>
+      </c>
       <c r="R504" s="2" t="s">
         <v>1507</v>
       </c>
-      <c r="S504" s="2"/>
+      <c r="S504" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T504" t="s">
         <v>2422</v>
       </c>
@@ -46054,7 +46094,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="505" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46096,12 +46136,18 @@
         <v>2389</v>
       </c>
       <c r="O505" s="2"/>
-      <c r="P505" s="2"/>
-      <c r="Q505" s="2"/>
+      <c r="P505" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q505" t="s">
+        <v>2455</v>
+      </c>
       <c r="R505" s="3" t="s">
         <v>1507</v>
       </c>
-      <c r="S505" s="2"/>
+      <c r="S505" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T505" t="s">
         <v>2422</v>
       </c>
@@ -46139,7 +46185,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="506" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46181,12 +46227,18 @@
         <v>2389</v>
       </c>
       <c r="O506" s="2"/>
-      <c r="P506" s="2"/>
-      <c r="Q506" s="2"/>
+      <c r="P506" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q506" t="s">
+        <v>2455</v>
+      </c>
       <c r="R506" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="S506" s="2"/>
+      <c r="S506" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T506" t="s">
         <v>2422</v>
       </c>
@@ -46224,7 +46276,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="507" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46309,7 +46361,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="508" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46394,7 +46446,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="509" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46479,7 +46531,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="510" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46564,7 +46616,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="511" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46649,7 +46701,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="512" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46734,7 +46786,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="513" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46819,7 +46871,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="514" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="2" t="s">
         <v>1479</v>
       </c>
@@ -46904,7 +46956,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="515" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="3" t="s">
         <v>1479</v>
       </c>
@@ -46942,12 +46994,18 @@
       </c>
       <c r="N515" s="2"/>
       <c r="O515" s="2"/>
-      <c r="P515" s="2"/>
-      <c r="Q515" s="2"/>
+      <c r="P515" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q515" t="s">
+        <v>2455</v>
+      </c>
       <c r="R515" s="3" t="s">
         <v>1487</v>
       </c>
-      <c r="S515" s="2"/>
+      <c r="S515" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T515" t="s">
         <v>2422</v>
       </c>
@@ -46985,7 +47043,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="516" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47023,12 +47081,18 @@
       </c>
       <c r="N516" s="2"/>
       <c r="O516" s="2"/>
-      <c r="P516" s="2"/>
-      <c r="Q516" s="2"/>
+      <c r="P516" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q516" t="s">
+        <v>2455</v>
+      </c>
       <c r="R516" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="S516" s="2"/>
+      <c r="S516" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T516" t="s">
         <v>2422</v>
       </c>
@@ -47066,7 +47130,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="517" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="3" t="s">
         <v>1479</v>
       </c>
@@ -47153,7 +47217,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="518" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47240,7 +47304,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="519" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="3" t="s">
         <v>1479</v>
       </c>
@@ -47323,7 +47387,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="520" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47406,7 +47470,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="521" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="3" t="s">
         <v>1479</v>
       </c>
@@ -47487,7 +47551,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="522" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47574,7 +47638,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="523" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="2" t="s">
         <v>1479</v>
       </c>
@@ -47661,7 +47725,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="524" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="3" t="s">
         <v>2023</v>
       </c>
@@ -47738,7 +47802,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="525" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="2" t="s">
         <v>2023</v>
       </c>
@@ -47819,7 +47883,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="526" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="3" t="s">
         <v>2023</v>
       </c>
@@ -47900,7 +47964,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="527" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="2" t="s">
         <v>2023</v>
       </c>
@@ -47981,7 +48045,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="528" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48062,7 +48126,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="529" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48143,7 +48207,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="530" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48224,7 +48288,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="531" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48299,7 +48363,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="532" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48380,7 +48444,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="533" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48467,7 +48531,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="534" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48554,7 +48618,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="535" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48641,7 +48705,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="536" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48728,7 +48792,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="537" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48811,7 +48875,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="538" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="3" t="s">
         <v>2023</v>
       </c>
@@ -48894,7 +48958,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="539" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="2" t="s">
         <v>2023</v>
       </c>
@@ -48977,7 +49041,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="540" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49060,7 +49124,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="541" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49143,7 +49207,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="542" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49226,7 +49290,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="543" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49309,7 +49373,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="544" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49392,7 +49456,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="545" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49477,7 +49541,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="546" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49562,7 +49626,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="547" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49647,7 +49711,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="548" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49718,7 +49782,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="549" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49805,7 +49869,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="550" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="3" t="s">
         <v>2023</v>
       </c>
@@ -49892,7 +49956,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="551" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="2" t="s">
         <v>2023</v>
       </c>
@@ -49967,7 +50031,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="552" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50042,7 +50106,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="553" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50117,7 +50181,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="554" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50204,7 +50268,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="555" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50279,7 +50343,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="556" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50354,7 +50418,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="557" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50425,7 +50489,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="558" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50496,7 +50560,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="559" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50583,7 +50647,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="560" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50670,7 +50734,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="561" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50708,12 +50772,18 @@
       </c>
       <c r="N561" s="2"/>
       <c r="O561" s="2"/>
-      <c r="P561" s="2"/>
-      <c r="Q561" s="2"/>
+      <c r="P561" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q561" t="s">
+        <v>2455</v>
+      </c>
       <c r="R561" s="2" t="s">
         <v>1905</v>
       </c>
-      <c r="S561" s="2"/>
+      <c r="S561" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T561" t="s">
         <v>2422</v>
       </c>
@@ -50751,7 +50821,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="562" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50789,12 +50859,18 @@
       </c>
       <c r="N562" s="2"/>
       <c r="O562" s="2"/>
-      <c r="P562" s="2"/>
-      <c r="Q562" s="2"/>
+      <c r="P562" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q562" t="s">
+        <v>2455</v>
+      </c>
       <c r="R562" s="3" t="s">
         <v>1905</v>
       </c>
-      <c r="S562" s="2"/>
+      <c r="S562" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T562" t="s">
         <v>2422</v>
       </c>
@@ -50832,7 +50908,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="563" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="2" t="s">
         <v>2023</v>
       </c>
@@ -50874,12 +50950,18 @@
         <v>2389</v>
       </c>
       <c r="O563" s="2"/>
-      <c r="P563" s="2"/>
-      <c r="Q563" s="2"/>
+      <c r="P563" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q563" t="s">
+        <v>2455</v>
+      </c>
       <c r="R563" s="2" t="s">
         <v>1905</v>
       </c>
-      <c r="S563" s="2"/>
+      <c r="S563" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T563" t="s">
         <v>2422</v>
       </c>
@@ -50917,7 +50999,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="564" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="3" t="s">
         <v>2023</v>
       </c>
@@ -50959,12 +51041,18 @@
         <v>2389</v>
       </c>
       <c r="O564" s="2"/>
-      <c r="P564" s="2"/>
-      <c r="Q564" s="2"/>
+      <c r="P564" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q564" t="s">
+        <v>2455</v>
+      </c>
       <c r="R564" s="3" t="s">
         <v>1905</v>
       </c>
-      <c r="S564" s="2"/>
+      <c r="S564" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T564" t="s">
         <v>2422</v>
       </c>
@@ -51002,7 +51090,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="565" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51040,12 +51128,18 @@
       </c>
       <c r="N565" s="2"/>
       <c r="O565" s="2"/>
-      <c r="P565" s="2"/>
-      <c r="Q565" s="2"/>
+      <c r="P565" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q565" t="s">
+        <v>2455</v>
+      </c>
       <c r="R565" s="2" t="s">
         <v>1905</v>
       </c>
-      <c r="S565" s="2"/>
+      <c r="S565" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T565" t="s">
         <v>2422</v>
       </c>
@@ -51083,7 +51177,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="566" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51172,7 +51266,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="567" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51261,7 +51355,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="568" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51350,7 +51444,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="569" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51439,7 +51533,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="570" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51528,7 +51622,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="571" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51613,7 +51707,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="572" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51698,7 +51792,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="573" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51783,7 +51877,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="574" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="3" t="s">
         <v>2023</v>
       </c>
@@ -51870,7 +51964,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="575" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="2" t="s">
         <v>2023</v>
       </c>
@@ -51957,7 +52051,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="576" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52044,7 +52138,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="577" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52127,7 +52221,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="578" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52206,7 +52300,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="579" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52280,7 +52374,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="580" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52352,7 +52446,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="581" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52426,7 +52520,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="582" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52468,12 +52562,18 @@
         <v>2389</v>
       </c>
       <c r="O582" s="2"/>
-      <c r="P582" s="2"/>
-      <c r="Q582" s="2"/>
+      <c r="P582" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q582" t="s">
+        <v>2455</v>
+      </c>
       <c r="R582" s="3" t="s">
         <v>1905</v>
       </c>
-      <c r="S582" s="2"/>
+      <c r="S582" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T582" t="s">
         <v>2422</v>
       </c>
@@ -52511,7 +52611,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="583" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52549,12 +52649,18 @@
       </c>
       <c r="N583" s="2"/>
       <c r="O583" s="2"/>
-      <c r="P583" s="2"/>
-      <c r="Q583" s="2"/>
+      <c r="P583" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q583" t="s">
+        <v>2455</v>
+      </c>
       <c r="R583" s="2" t="s">
         <v>1866</v>
       </c>
-      <c r="S583" s="2"/>
+      <c r="S583" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T583" t="s">
         <v>2422</v>
       </c>
@@ -52592,7 +52698,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="584" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52630,12 +52736,18 @@
       </c>
       <c r="N584" s="2"/>
       <c r="O584" s="2"/>
-      <c r="P584" s="2"/>
-      <c r="Q584" s="2"/>
+      <c r="P584" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q584" t="s">
+        <v>2455</v>
+      </c>
       <c r="R584" s="3" t="s">
         <v>1905</v>
       </c>
-      <c r="S584" s="2"/>
+      <c r="S584" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T584" t="s">
         <v>2422</v>
       </c>
@@ -52673,7 +52785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="585" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52711,12 +52823,18 @@
       </c>
       <c r="N585" s="2"/>
       <c r="O585" s="2"/>
-      <c r="P585" s="2"/>
-      <c r="Q585" s="2"/>
+      <c r="P585" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q585" t="s">
+        <v>2455</v>
+      </c>
       <c r="R585" s="2" t="s">
         <v>1866</v>
       </c>
-      <c r="S585" s="2"/>
+      <c r="S585" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T585" t="s">
         <v>2422</v>
       </c>
@@ -52754,7 +52872,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="586" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52829,7 +52947,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="587" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="2" t="s">
         <v>2023</v>
       </c>
@@ -52904,7 +53022,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="588" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="3" t="s">
         <v>2023</v>
       </c>
@@ -52991,7 +53109,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="589" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="2" t="s">
         <v>2023</v>
       </c>
@@ -53078,7 +53196,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="590" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="8" t="s">
         <v>292</v>
       </c>
@@ -53153,7 +53271,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="591" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="8" t="s">
         <v>32</v>
       </c>
@@ -53250,11 +53368,13 @@
       <c r="I592" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="J592" s="2"/>
+      <c r="J592" t="s">
+        <v>2452</v>
+      </c>
       <c r="K592" s="2"/>
       <c r="L592" s="2"/>
-      <c r="M592" s="2" t="s">
-        <v>2452</v>
+      <c r="M592" t="s">
+        <v>2453</v>
       </c>
       <c r="N592" s="2"/>
       <c r="O592" s="2"/>
@@ -53295,7 +53415,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="593" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="8" t="s">
         <v>594</v>
       </c>
@@ -53364,7 +53484,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="594" spans="1:31" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="8" t="s">
         <v>1479</v>
       </c>
@@ -53403,12 +53523,18 @@
         <v>2389</v>
       </c>
       <c r="O594" s="2"/>
-      <c r="P594" s="2"/>
-      <c r="Q594" s="2"/>
+      <c r="P594" t="s">
+        <v>2454</v>
+      </c>
+      <c r="Q594" t="s">
+        <v>2455</v>
+      </c>
       <c r="R594" s="3" t="s">
         <v>1905</v>
       </c>
-      <c r="S594" s="2"/>
+      <c r="S594" s="2" t="s">
+        <v>1741</v>
+      </c>
       <c r="T594" t="s">
         <v>2422</v>
       </c>
@@ -53483,14 +53609,6 @@
     <row r="629" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="630" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:AE594" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="MANGALORE"/>
-        <filter val="UDIPI"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/CFA-Stockist-HQ_Mapping_Master_Updated.xlsx
+++ b/CFA-Stockist-HQ_Mapping_Master_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milind\Desktop\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D102F88F-8C88-4F92-A56D-FEE38FEF4491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60B8794-7220-451F-9B44-C93F8C3DDC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="CFA-Stockist-HQ Mapping" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CFA-Stockist-HQ Mapping'!$A$1:$AE$594</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CFA-Stockist-HQ Mapping'!$A$1:$AE$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53609,6 +53609,7 @@
     <row r="629" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="630" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <autoFilter ref="A1:AE1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>